--- a/Russian Dictionary.xlsx
+++ b/Russian Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="2383">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -6574,6 +6574,597 @@
   </si>
   <si>
     <t>unit 19</t>
+  </si>
+  <si>
+    <t>what do you have today?</t>
+  </si>
+  <si>
+    <t>что у вас есть сегодня?</t>
+  </si>
+  <si>
+    <t>chtoh oh vas yest' se-vohd-nya?</t>
+  </si>
+  <si>
+    <t>for the gentleman</t>
+  </si>
+  <si>
+    <t>для джентльмена</t>
+  </si>
+  <si>
+    <t>dleh djentelmenah</t>
+  </si>
+  <si>
+    <t>you speak more quickly</t>
+  </si>
+  <si>
+    <t>вы говорите быстрее</t>
+  </si>
+  <si>
+    <t>vy gavarite bys-treyeh</t>
+  </si>
+  <si>
+    <t>I speak quickly when I speak Russian</t>
+  </si>
+  <si>
+    <t>я говорю быстро когда я говорю по-русски</t>
+  </si>
+  <si>
+    <t>ya gavaryou bystra kagda ya gavaryu pa-russki</t>
+  </si>
+  <si>
+    <t>I have 50 thousand rubles</t>
+  </si>
+  <si>
+    <t>у меня пятьдесят тысяч рублей</t>
+  </si>
+  <si>
+    <t>oh menya peet-desyat ty-setch rubleh</t>
+  </si>
+  <si>
+    <t>41 thousand rubles</t>
+  </si>
+  <si>
+    <t>сорок одна тысяча рублей</t>
+  </si>
+  <si>
+    <t>sorak adna ty-setchah rubleh</t>
+  </si>
+  <si>
+    <t>62 thousand rubles</t>
+  </si>
+  <si>
+    <t>шестьдесят две тысячи рублей</t>
+  </si>
+  <si>
+    <t>chest-desyat dveh ty-setchi rubleh</t>
+  </si>
+  <si>
+    <t>56 thousand rubles</t>
+  </si>
+  <si>
+    <t>пятьдесят шесть тысяч рублей</t>
+  </si>
+  <si>
+    <t>peet-desyat shest' ty-setch rubleh</t>
+  </si>
+  <si>
+    <t>семьдесят семь</t>
+  </si>
+  <si>
+    <t>sem'desyat sem'</t>
+  </si>
+  <si>
+    <t>68, that's too expensive!</t>
+  </si>
+  <si>
+    <t>chest-desyat vosem', etah slee-shkam doh-raga!</t>
+  </si>
+  <si>
+    <t>шестьдесят восемь, это слишком дорого!</t>
+  </si>
+  <si>
+    <t>I am going to give you</t>
+  </si>
+  <si>
+    <t>я собираюсь дать вам</t>
+  </si>
+  <si>
+    <t>ya sabi-rayus' dat vam</t>
+  </si>
+  <si>
+    <t>I am going to give you 53 thousand rubles</t>
+  </si>
+  <si>
+    <t>я собираюсь дать вам пятьдесят три тысячи рублей</t>
+  </si>
+  <si>
+    <t>ya sabi-rayus' dat vam peet-desyat tri ty-setchi rubleh</t>
+  </si>
+  <si>
+    <t>where's your husband?</t>
+  </si>
+  <si>
+    <t>gdieh vash moj?</t>
+  </si>
+  <si>
+    <t>где ваш муж?</t>
+  </si>
+  <si>
+    <t>мой муж там</t>
+  </si>
+  <si>
+    <t>moy moj tam</t>
+  </si>
+  <si>
+    <t>my husband is over there</t>
+  </si>
+  <si>
+    <t>he's over there</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>он там</t>
+  </si>
+  <si>
+    <t>on tam</t>
+  </si>
+  <si>
+    <t>он</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>my husband, he's over there</t>
+  </si>
+  <si>
+    <t>мой муж, он там</t>
+  </si>
+  <si>
+    <t>moy moj, on tam</t>
+  </si>
+  <si>
+    <t>she's over there</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>она</t>
+  </si>
+  <si>
+    <t>ana</t>
+  </si>
+  <si>
+    <t>она там</t>
+  </si>
+  <si>
+    <t>ana tam</t>
+  </si>
+  <si>
+    <t>my wife, she's over there</t>
+  </si>
+  <si>
+    <t>моя жена, она там</t>
+  </si>
+  <si>
+    <t>maya jenah, ana tam</t>
+  </si>
+  <si>
+    <t>she's over there?</t>
+  </si>
+  <si>
+    <t>она там?</t>
+  </si>
+  <si>
+    <t>ana tam?</t>
+  </si>
+  <si>
+    <t>I don't know where she's</t>
+  </si>
+  <si>
+    <t>я не знаю где она</t>
+  </si>
+  <si>
+    <t>ya ne znayu gdieh ana</t>
+  </si>
+  <si>
+    <t>what does your husband want to drink?</t>
+  </si>
+  <si>
+    <t>что ваш муж хочет пить?</t>
+  </si>
+  <si>
+    <t>chtoh vash moj khotchet peet'?</t>
+  </si>
+  <si>
+    <t>what does he want to drink?</t>
+  </si>
+  <si>
+    <t>что он хочет пить?</t>
+  </si>
+  <si>
+    <t>chtoh on khotchet peet'?</t>
+  </si>
+  <si>
+    <t>he wants some milk</t>
+  </si>
+  <si>
+    <t>он хочет немного молока</t>
+  </si>
+  <si>
+    <t>on khotchet nemnoga malakah</t>
+  </si>
+  <si>
+    <t>or some water</t>
+  </si>
+  <si>
+    <t>eeleeh nemnoga vady</t>
+  </si>
+  <si>
+    <t>или немного воды</t>
+  </si>
+  <si>
+    <t>come in</t>
+  </si>
+  <si>
+    <t>войдите</t>
+  </si>
+  <si>
+    <t>pleased to meet you!</t>
+  </si>
+  <si>
+    <t>ochen' priyatna!</t>
+  </si>
+  <si>
+    <t>очень приятно!</t>
+  </si>
+  <si>
+    <t>madam</t>
+  </si>
+  <si>
+    <t>мадам</t>
+  </si>
+  <si>
+    <t>sir</t>
+  </si>
+  <si>
+    <t>сэр</t>
+  </si>
+  <si>
+    <t>ser</t>
+  </si>
+  <si>
+    <t>pleased to meet you madam!</t>
+  </si>
+  <si>
+    <t>очень приятно мадам!</t>
+  </si>
+  <si>
+    <t>ochen' priyatna madam!</t>
+  </si>
+  <si>
+    <t>is your wife also here?</t>
+  </si>
+  <si>
+    <t>ваша жена тоже здесь?</t>
+  </si>
+  <si>
+    <t>vashah jenah tojah zdes'?</t>
+  </si>
+  <si>
+    <t>no, she's in the restaurant</t>
+  </si>
+  <si>
+    <t>niet, ana v restoraneh</t>
+  </si>
+  <si>
+    <t>нет, она в ресторане</t>
+  </si>
+  <si>
+    <t>come in please</t>
+  </si>
+  <si>
+    <t>войдите пожалуйста</t>
+  </si>
+  <si>
+    <t>what does she want to drink?</t>
+  </si>
+  <si>
+    <t>что она хочет пить?</t>
+  </si>
+  <si>
+    <t>chtoh ana khotchet peet'?</t>
+  </si>
+  <si>
+    <t>where do you live?</t>
+  </si>
+  <si>
+    <t>you live</t>
+  </si>
+  <si>
+    <t>I live</t>
+  </si>
+  <si>
+    <t>я живу</t>
+  </si>
+  <si>
+    <t>я живу на Тверской улице</t>
+  </si>
+  <si>
+    <t>I live on Tverskaya street</t>
+  </si>
+  <si>
+    <t>do you live here?</t>
+  </si>
+  <si>
+    <t>yes, we live here</t>
+  </si>
+  <si>
+    <t>we live</t>
+  </si>
+  <si>
+    <t>мы живём</t>
+  </si>
+  <si>
+    <t>да, мы живём здесь</t>
+  </si>
+  <si>
+    <t>we want</t>
+  </si>
+  <si>
+    <t>мы хотим</t>
+  </si>
+  <si>
+    <t>my khatim</t>
+  </si>
+  <si>
+    <t>but we want to drink something over there</t>
+  </si>
+  <si>
+    <t>но мы хотим пить кое-что там</t>
+  </si>
+  <si>
+    <t>no my khatim peet' koweh-chto tam</t>
+  </si>
+  <si>
+    <t>мы с мужем</t>
+  </si>
+  <si>
+    <t>my s mojem</t>
+  </si>
+  <si>
+    <t>my husband and I (we with husband)</t>
+  </si>
+  <si>
+    <t>мы не живём здесь</t>
+  </si>
+  <si>
+    <t>we don't live here</t>
+  </si>
+  <si>
+    <t>my husband and I want some milk</t>
+  </si>
+  <si>
+    <t>мы с мужем хотим немного молока</t>
+  </si>
+  <si>
+    <t>my s mojem khatim nemnoga malakah</t>
+  </si>
+  <si>
+    <t>you also want some milk?</t>
+  </si>
+  <si>
+    <t>вы тоже хотите немного молока?</t>
+  </si>
+  <si>
+    <t>vy tojah khatite nemnoga malakah?</t>
+  </si>
+  <si>
+    <t>we want some water</t>
+  </si>
+  <si>
+    <t>мы хотим немного воды</t>
+  </si>
+  <si>
+    <t>my khatim nemnoga vady</t>
+  </si>
+  <si>
+    <t>he's not here</t>
+  </si>
+  <si>
+    <t>он не здесь</t>
+  </si>
+  <si>
+    <t>on né zdes'</t>
+  </si>
+  <si>
+    <t>where's he?</t>
+  </si>
+  <si>
+    <t>где он?</t>
+  </si>
+  <si>
+    <t>gdieh on?</t>
+  </si>
+  <si>
+    <t>he's on Pushkin street</t>
+  </si>
+  <si>
+    <t>он на пушкинской улице</t>
+  </si>
+  <si>
+    <t>on na Pushkinskoy olitsa</t>
+  </si>
+  <si>
+    <t>he wants to buy something</t>
+  </si>
+  <si>
+    <t>он хочет купить кое-что</t>
+  </si>
+  <si>
+    <t>on khotchet kopeet' koweh-chto</t>
+  </si>
+  <si>
+    <t>when will he be here?</t>
+  </si>
+  <si>
+    <t>когда он будет здесь?</t>
+  </si>
+  <si>
+    <t>kagda on bodet zdes'?</t>
+  </si>
+  <si>
+    <t>where do you live in America?</t>
+  </si>
+  <si>
+    <t>где вы живёте?</t>
+  </si>
+  <si>
+    <t>вы живёте</t>
+  </si>
+  <si>
+    <t>вы живёте здесь?</t>
+  </si>
+  <si>
+    <t>где вы живёте в Америке?</t>
+  </si>
+  <si>
+    <t>я живу в Вашингтоне</t>
+  </si>
+  <si>
+    <t>I live in Washington</t>
+  </si>
+  <si>
+    <t>we live in Washington</t>
+  </si>
+  <si>
+    <t>мы живём в Вашингтоне</t>
+  </si>
+  <si>
+    <t>my husband and I live in Washington</t>
+  </si>
+  <si>
+    <t>мы с мужем живём в Вашингтоне</t>
+  </si>
+  <si>
+    <t>and you? Where do you live?</t>
+  </si>
+  <si>
+    <t>а вы? где вы живёте?</t>
+  </si>
+  <si>
+    <t>yah ji-voh</t>
+  </si>
+  <si>
+    <t>yah ji-voh na Tverskoy olitsa</t>
+  </si>
+  <si>
+    <t>da, my jiv-yom zdes'</t>
+  </si>
+  <si>
+    <t>my jiv-yom</t>
+  </si>
+  <si>
+    <t>my né jiv-yom zdes'</t>
+  </si>
+  <si>
+    <t>yah ji-voh vashingtonieh</t>
+  </si>
+  <si>
+    <t>my jiv-yom vashingtonieh</t>
+  </si>
+  <si>
+    <t>my s mojem jiv-yom vashingtonieh</t>
+  </si>
+  <si>
+    <t>I live in Moscow</t>
+  </si>
+  <si>
+    <t>я живу в Москве</t>
+  </si>
+  <si>
+    <t>yah ji-voh v mask-veh</t>
+  </si>
+  <si>
+    <t>that's my husband, he's here</t>
+  </si>
+  <si>
+    <t>это мой муж, он здесь</t>
+  </si>
+  <si>
+    <t>etah moy moj, on zdes'</t>
+  </si>
+  <si>
+    <t>what does he want?</t>
+  </si>
+  <si>
+    <t>что он хочет?</t>
+  </si>
+  <si>
+    <t>chtoh on khotchet?</t>
+  </si>
+  <si>
+    <t>he wants beer</t>
+  </si>
+  <si>
+    <t>on khotchet piva</t>
+  </si>
+  <si>
+    <t>он хочет пиво</t>
+  </si>
+  <si>
+    <t>give me two beers please</t>
+  </si>
+  <si>
+    <t>дайте мне два пива пожалуйста</t>
+  </si>
+  <si>
+    <t>daiete mnieh dva piva pajaluysta</t>
+  </si>
+  <si>
+    <t>now we can talk</t>
+  </si>
+  <si>
+    <t>we can</t>
+  </si>
+  <si>
+    <t>мы можем</t>
+  </si>
+  <si>
+    <t>my mojem</t>
+  </si>
+  <si>
+    <t>сейчас мы можем говорить</t>
+  </si>
+  <si>
+    <t>seetchas my mojem gava-reet</t>
+  </si>
+  <si>
+    <t>unit 20</t>
+  </si>
+  <si>
+    <t>gdieh vy jiv-yoh-tieh?</t>
+  </si>
+  <si>
+    <t>vy jiv-yoh-tieh</t>
+  </si>
+  <si>
+    <t>vy jiv-yoh-tieh zdes'?</t>
+  </si>
+  <si>
+    <t>gdieh vy jiv-yoh-tieh v Amerikeh?</t>
+  </si>
+  <si>
+    <t>a vy? gdieh vy jiv-yoh-tieh?</t>
+  </si>
+  <si>
+    <t>vay-deeteh</t>
+  </si>
+  <si>
+    <t>vay-deeteh pajaluysta</t>
   </si>
 </sst>
 </file>
@@ -6621,7 +7212,1087 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="923">
+  <dxfs count="1031">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -16149,7 +17820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D739"/>
+  <dimension ref="B1:D806"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -24222,2613 +25893,3830 @@
         <v>2185</v>
       </c>
     </row>
+    <row r="740" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B740" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C740" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D740" s="1" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="741" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B741" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C741" s="1" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D741" s="1" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="742" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B742" s="1" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="743" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B743" s="1" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="744" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B744" s="1" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C744" s="1" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D744" s="1" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="745" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B745" s="1" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C745" s="1" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D745" s="1" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="746" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B746" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="747" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B747" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C747" s="1" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="748" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B748" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C748" s="1" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D748" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="749" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B749" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C749" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="750" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B750" s="1" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="751" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B751" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="752" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B752" s="1" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C752" s="1" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="753" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B753" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C753" s="1" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="754" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B754" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C754" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="755" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B755" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C755" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="756" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B756" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C756" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="757" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B757" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="758" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B758" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="759" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B759" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C759" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="760" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B760" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C760" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="761" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B761" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="762" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B762" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="763" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B763" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C763" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="764" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B764" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="765" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B765" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C765" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="766" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B766" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="767" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B767" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C767" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="768" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B768" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="769" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B769" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="770" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B770" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="771" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B771" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="772" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B772" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="773" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B773" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C773" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="774" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B774" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C774" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="775" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B775" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="776" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B776" s="1" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="777" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B777" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="778" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B778" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="779" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B779" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="780" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B780" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="781" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B781" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="782" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B782" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="783" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B783" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C783" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="784" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B784" s="1" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C784" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="785" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B785" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C785" s="1" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="786" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B786" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C786" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="787" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B787" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C787" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="788" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B788" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C788" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="789" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B789" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C789" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="790" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B790" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C790" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="791" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B791" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C791" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="792" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B792" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C792" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="793" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B793" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C793" s="1" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="794" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B794" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C794" s="1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="795" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B795" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C795" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="796" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B796" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C796" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="797" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B797" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C797" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="798" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B798" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C798" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="799" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B799" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C799" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="800" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B800" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C800" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="801" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B801" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C801" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="802" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B802" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C802" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="803" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B803" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C803" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="804" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B804" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C804" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="805" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B805" s="1" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C805" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="806" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B806" s="1" t="s">
+        <v>2375</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="904" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124">
-    <cfRule type="duplicateValues" dxfId="903" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="902" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="901" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="900" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="899" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="898" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="897" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="896" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="895" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="894" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="893" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="892" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="891" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="890" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="889" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="888" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="887" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="886" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="885" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="884" priority="1260"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="883" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="882" priority="1258"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="881" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="880" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="879" priority="1255"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="878" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="877" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="876" priority="1252"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="875" priority="1251"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="874" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="873" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="872" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="871" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="870" priority="1246"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="869" priority="1245"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="868" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="867" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="866" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="865" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="864" priority="1240"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="863" priority="1239"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="862" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="861" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="860" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="859" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="858" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="857" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="856" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="855" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="854" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="853" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="852" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="851" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="850" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="849" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="848" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="847" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="846" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="845" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="844" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="843" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="842" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="841" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="840" priority="1216"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="839" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="838" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="837" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="836" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="835" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="834" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="833" priority="1208"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="832" priority="1207"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="831" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="830" priority="1205"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="829" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="828" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="827" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="826" priority="1201"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="825" priority="1200"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="824" priority="1199"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="823" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="822" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="821" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="820" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="819" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="818" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="817" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="816" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="815" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="814" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="813" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="812" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="811" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="810" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="809" priority="1182"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="808" priority="1181"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="807" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="806" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="805" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="804" priority="1177"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="803" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="802" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="801" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="800" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="799" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="798" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="797" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="796" priority="1169"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="795" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="794" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="793" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="792" priority="1165"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="791" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="790" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="789" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="788" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="787" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="786" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="785" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="784" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="783" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="782" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="781" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="780" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="779" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="778" priority="1147"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="777" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="776" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="775" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="774" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="773" priority="1142"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="772" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="771" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="770" priority="1137"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="769" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="768" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="767" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="766" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="765" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="764" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="763" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="762" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="761" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="760" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="759" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="758" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="757" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="756" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="755" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="754" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="753" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="752" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="751" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="750" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="749" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="748" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="747" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="746" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="745" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="744" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="743" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="742" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="741" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="740" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="739" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="738" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="737" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="736" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="735" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="734" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="733" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="732" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="731" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="730" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="729" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="728" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="727" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="726" priority="1072"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="725" priority="1071"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="724" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="723" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="722" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="721" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="720" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="719" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="718" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="717" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="716" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="715" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="714" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="713" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="712" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="711" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="710" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="709" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="708" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="707" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="706" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="705" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="704" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="703" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="702" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="701" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="700" priority="1026"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="699" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="698" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="697" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="696" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="695" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="694" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="693" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="692" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="691" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="690" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="689" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="688" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="687" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="686" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="685" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="684" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="683" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="682" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="681" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="680" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="679" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="678" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="677" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="676" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="675" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="674" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="673" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="672" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="671" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="670" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="669" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="668" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="667" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="666" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="665" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="664" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="663" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="662" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="661" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="660" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="659" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="658" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="657" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="656" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="655" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="654" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="653" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="652" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="651" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="650" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="649" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="1227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="648" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="647" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="646" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="645" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="644" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="643" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="642" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="641" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="640" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="1212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="639" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="1211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="638" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="637" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="1209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="636" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="635" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="1203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="634" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="633" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="1197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="632" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="631" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="630" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="1194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="629" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="1193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="628" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="627" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="1191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="626" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="625" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="624" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="1186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="623" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="1185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="622" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="621" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="1183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="620" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="1182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="619" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="1181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="618" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="617" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="616" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="1176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="615" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="1175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="614" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="1174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="613" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="1173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="612" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="611" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="1171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="610" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="1170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="609" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="1169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="608" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="607" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="606" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="1166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="605" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="1165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="604" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="1164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="603" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="1163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="602" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="1162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="601" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="600" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="599" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="598" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="597" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="596" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="595" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="1155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="594" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="593" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="592" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="591" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="590" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="1146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="589" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="1145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="588" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="1140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="587" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="1139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="586" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="585" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="584" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="1134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="583" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="582" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="1132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="581" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="1131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="580" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="579" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="1129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="578" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="577" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="1127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="576" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="575" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="574" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="573" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="572" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="1120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="571" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="570" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="569" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="568" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="1116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="567" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="566" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="565" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="1113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="564" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="1112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="563" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="1111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="562" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="561" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="560" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="559" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="558" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="557" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="556" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="555" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="554" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="553" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="1095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="552" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="1094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="551" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="1093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="550" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="1092"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="549" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="1091"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="548" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="1090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="547" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="546" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="1088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="545" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="1087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="544" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="543" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="542" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="1082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="541" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="540" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="539" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="538" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="1078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="537" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="1077"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="536" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="1076"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="535" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="1075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="534" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="533" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="532" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="1070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="531" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="1069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="530" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="529" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="528" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="1062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="527" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="1061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="526" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="1058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="525" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="524" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="523" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="522" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="1054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="521" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="520" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="1052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="519" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="518" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="517" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="516" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="515" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="1045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="514" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="513" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="512" priority="766"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="511" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="510" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="509" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="1039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="508" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="1036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="507" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="1035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="506" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="1034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="505" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="504" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="503" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="502" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="501" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="1027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="500" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="499" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="498" priority="740"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="497" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="1015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="496" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="495" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="494" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="493" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="1011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="492" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="1008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="491" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="1007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="490" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="489" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="488" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="487" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="486" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="485" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="484" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="483" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="482" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="481" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="480" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="479" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="478" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="477" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="476" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="475" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="474" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="473" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="472" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="970"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="471" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="470" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="469" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="468" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="467" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="466" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="465" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="464" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="463" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="462" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="461" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="460" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="459" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="951"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="458" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="457" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="456" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="455" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="454" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="453" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="943"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="452" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="451" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="450" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="940"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="449" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="448" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="447" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="446" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="445" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="444" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="443" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="442" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="441" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="440" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="439" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="438" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="437" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="436" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="435" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="434" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="433" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="432" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="431" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="899"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="430" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="429" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="428" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="427" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="426" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="425" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="424" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="423" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="422" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="421" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="420" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="419" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="418" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="417" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="416" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="415" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="414" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="413" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="412" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="411" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="410" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="409" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="408" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="407" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="406" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="405" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="404" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="403" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="402" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="401" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="400" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="399" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="398" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="397" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="396" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="395" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="394" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="393" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="392" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="391" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="390" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="389" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="388" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="387" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="386" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="385" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="384" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="383" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="382" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="381" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="380" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="379" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="378" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="377" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="376" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="375" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="374" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="373" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="372" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="371" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="370" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="369" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="368" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="367" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="366" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="365" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="364" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="363" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="362" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="361" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="360" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="359" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="358" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="357" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="356" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="355" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="354" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="353" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="761"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="352" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="351" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="350" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="758"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="349" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="348" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="347" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="346" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="345" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="344" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="343" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="342" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="341" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="340" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="339" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="338" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="337" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="336" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="335" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="334" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="333" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="332" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="331" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="330" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="329" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="328" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="327" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="326" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="325" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="324" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="323" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="322" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="321" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="320" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="319" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="318" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="317" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="316" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="315" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="314" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="313" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="312" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="311" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="310" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="309" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="308" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="307" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="306" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="305" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="304" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="303" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="302" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="301" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="300" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="299" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="298" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="297" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="296" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="295" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="294" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="293" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="292" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="291" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="290" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="289" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="288" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="287" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="286" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="285" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="284" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="283" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="282" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="281" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="280" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="279" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="278" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="277" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="276" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="275" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="274" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="273" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="272" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="271" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="270" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="269" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="268" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="267" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="266" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="265" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="264" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="263" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="262" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="261" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="260" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="259" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="258" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="257" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="256" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="255" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="254" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="253" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="252" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="251" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="250" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="249" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="248" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="247" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="246" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="245" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="244" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="243" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="242" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="241" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="240" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="239" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="238" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="237" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="236" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="235" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="234" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="233" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="232" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="231" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="230" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="229" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="228" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="227" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="226" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="225" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="224" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="223" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="222" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="221" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="220" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="219" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="218" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="217" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="216" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="215" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="214" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="213" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="212" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="211" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="210" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="209" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="208" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="207" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="206" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="205" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="204" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="203" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="202" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="201" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="200" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="199" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="198" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="197" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="196" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="195" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="194" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="193" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="192" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="191" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="190" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="189" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="188" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="187" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="186" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="185" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="184" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="183" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="182" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="181" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="180" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="179" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="178" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="177" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="176" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="175" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="174" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="173" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="172" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="171" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="170" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="169" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="168" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="167" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="166" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="165" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="164" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="163" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="162" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="161" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="160" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="159" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="158" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="157" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="156" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="155" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="154" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="153" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="152" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="151" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="150" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="149" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="148" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="147" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="146" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="145" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="144" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="143" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="142" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="141" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="140" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="139" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="138" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="137" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="136" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="135" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="134" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="133" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="132" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="131" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="130" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="129" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="128" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="127" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="126" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="125" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="124" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="123" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="121" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="120" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="119" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="118" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="117" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="116" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="115" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="114" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="113" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="112" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="110" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="109" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="108" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="105" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="103" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="102" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="101" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="100" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="99" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="98" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="97" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="95" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="94" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="93" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="92" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="91" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="90" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="89" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="87" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="86" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="85" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="84" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="82" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="81" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="80" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="77" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="76" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="74" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="73" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="72" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="71" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="70" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="69" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="68" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="67" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="66" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="65" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="64" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="63" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="61" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="60" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="59" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="58" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="57" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739:B1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="1373"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739:B1048576">
-    <cfRule type="duplicateValues" dxfId="55" priority="1485"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739:B1048576">
-    <cfRule type="duplicateValues" dxfId="54" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="307"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
+    <cfRule type="duplicateValues" dxfId="182" priority="1649"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
+    <cfRule type="duplicateValues" dxfId="181" priority="1761"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
+    <cfRule type="duplicateValues" dxfId="180" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="53" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="51" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="49" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="41" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="35" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="31" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="277"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B740">
+    <cfRule type="duplicateValues" dxfId="161" priority="272"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B740">
+    <cfRule type="duplicateValues" dxfId="160" priority="273"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B741">
+    <cfRule type="duplicateValues" dxfId="159" priority="270"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B741">
+    <cfRule type="duplicateValues" dxfId="158" priority="269"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B741">
+    <cfRule type="duplicateValues" dxfId="157" priority="271"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B742">
+    <cfRule type="duplicateValues" dxfId="156" priority="263"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B742">
+    <cfRule type="duplicateValues" dxfId="155" priority="264"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B742">
+    <cfRule type="duplicateValues" dxfId="154" priority="265"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B743">
+    <cfRule type="duplicateValues" dxfId="153" priority="260"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B743">
+    <cfRule type="duplicateValues" dxfId="152" priority="261"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B743">
+    <cfRule type="duplicateValues" dxfId="151" priority="262"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B744">
+    <cfRule type="duplicateValues" dxfId="150" priority="254"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B744">
+    <cfRule type="duplicateValues" dxfId="149" priority="255"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B744">
+    <cfRule type="duplicateValues" dxfId="148" priority="256"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="147" priority="239"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="146" priority="240"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B745">
+    <cfRule type="duplicateValues" dxfId="145" priority="241"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B746">
+    <cfRule type="duplicateValues" dxfId="144" priority="233"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B746">
+    <cfRule type="duplicateValues" dxfId="143" priority="234"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B746">
+    <cfRule type="duplicateValues" dxfId="142" priority="235"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B747">
+    <cfRule type="duplicateValues" dxfId="141" priority="227"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B747">
+    <cfRule type="duplicateValues" dxfId="140" priority="228"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B747">
+    <cfRule type="duplicateValues" dxfId="139" priority="229"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B748">
+    <cfRule type="duplicateValues" dxfId="138" priority="225"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B748">
+    <cfRule type="duplicateValues" dxfId="137" priority="226"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B748">
+    <cfRule type="duplicateValues" dxfId="136" priority="224"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B749">
+    <cfRule type="duplicateValues" dxfId="135" priority="215"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B749">
+    <cfRule type="duplicateValues" dxfId="134" priority="216"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B749">
+    <cfRule type="duplicateValues" dxfId="133" priority="217"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="132" priority="207"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="131" priority="206"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B750">
+    <cfRule type="duplicateValues" dxfId="130" priority="208"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B751">
+    <cfRule type="duplicateValues" dxfId="129" priority="204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B751">
+    <cfRule type="duplicateValues" dxfId="128" priority="203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B751">
+    <cfRule type="duplicateValues" dxfId="127" priority="205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="126" priority="198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="125" priority="199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B752">
+    <cfRule type="duplicateValues" dxfId="124" priority="197"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753">
+    <cfRule type="duplicateValues" dxfId="123" priority="191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753">
+    <cfRule type="duplicateValues" dxfId="122" priority="192"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B753">
+    <cfRule type="duplicateValues" dxfId="121" priority="193"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="120" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="119" priority="189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B754">
+    <cfRule type="duplicateValues" dxfId="118" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="117" priority="185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="116" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B756">
+    <cfRule type="duplicateValues" dxfId="115" priority="187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="114" priority="182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="113" priority="183"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B757">
+    <cfRule type="duplicateValues" dxfId="112" priority="184"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="111" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="110" priority="180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B759">
+    <cfRule type="duplicateValues" dxfId="109" priority="179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="108" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="107" priority="177"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B760">
+    <cfRule type="duplicateValues" dxfId="106" priority="178"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761">
+    <cfRule type="duplicateValues" dxfId="105" priority="173"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761">
+    <cfRule type="duplicateValues" dxfId="104" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761">
+    <cfRule type="duplicateValues" dxfId="103" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="102" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="101" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B764">
+    <cfRule type="duplicateValues" dxfId="100" priority="170"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B762">
+    <cfRule type="duplicateValues" dxfId="99" priority="168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B762">
+    <cfRule type="duplicateValues" dxfId="98" priority="169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B763">
+    <cfRule type="duplicateValues" dxfId="97" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B763">
+    <cfRule type="duplicateValues" dxfId="96" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B765">
+    <cfRule type="duplicateValues" dxfId="95" priority="158"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B765">
+    <cfRule type="duplicateValues" dxfId="94" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B765">
+    <cfRule type="duplicateValues" dxfId="93" priority="157"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="92" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="91" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B767">
+    <cfRule type="duplicateValues" dxfId="90" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="89" priority="151"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="88" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B770">
+    <cfRule type="duplicateValues" dxfId="87" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B771">
+    <cfRule type="duplicateValues" dxfId="86" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B771">
+    <cfRule type="duplicateValues" dxfId="85" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B771">
+    <cfRule type="duplicateValues" dxfId="84" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B772">
+    <cfRule type="duplicateValues" dxfId="83" priority="145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B772">
+    <cfRule type="duplicateValues" dxfId="82" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B772">
+    <cfRule type="duplicateValues" dxfId="81" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B773">
+    <cfRule type="duplicateValues" dxfId="80" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B773">
+    <cfRule type="duplicateValues" dxfId="79" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B773">
+    <cfRule type="duplicateValues" dxfId="78" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B774">
+    <cfRule type="duplicateValues" dxfId="77" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B774">
+    <cfRule type="duplicateValues" dxfId="76" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="75" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="74" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B777">
+    <cfRule type="duplicateValues" dxfId="73" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B778">
+    <cfRule type="duplicateValues" dxfId="72" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B778">
+    <cfRule type="duplicateValues" dxfId="71" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B778">
+    <cfRule type="duplicateValues" dxfId="70" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B779">
+    <cfRule type="duplicateValues" dxfId="69" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B779">
+    <cfRule type="duplicateValues" dxfId="68" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B779">
+    <cfRule type="duplicateValues" dxfId="67" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B780">
+    <cfRule type="duplicateValues" dxfId="66" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B780">
+    <cfRule type="duplicateValues" dxfId="65" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B780">
+    <cfRule type="duplicateValues" dxfId="64" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="63" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="62" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784">
+    <cfRule type="duplicateValues" dxfId="61" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B785">
+    <cfRule type="duplicateValues" dxfId="60" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B785">
+    <cfRule type="duplicateValues" dxfId="59" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B785">
+    <cfRule type="duplicateValues" dxfId="58" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="57" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="56" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786">
+    <cfRule type="duplicateValues" dxfId="55" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B787">
+    <cfRule type="duplicateValues" dxfId="54" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B787">
+    <cfRule type="duplicateValues" dxfId="53" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B787">
+    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B788">
+    <cfRule type="duplicateValues" dxfId="51" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B788">
+    <cfRule type="duplicateValues" dxfId="50" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B788">
+    <cfRule type="duplicateValues" dxfId="49" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="48" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="47" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B789">
+    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B790">
+    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B790">
+    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B790">
+    <cfRule type="duplicateValues" dxfId="43" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B791">
+    <cfRule type="duplicateValues" dxfId="42" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B791">
+    <cfRule type="duplicateValues" dxfId="41" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B791">
+    <cfRule type="duplicateValues" dxfId="40" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B792">
+    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B792">
+    <cfRule type="duplicateValues" dxfId="38" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B792">
+    <cfRule type="duplicateValues" dxfId="37" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B793">
+    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B793">
+    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B793">
+    <cfRule type="duplicateValues" dxfId="34" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="33" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B794">
+    <cfRule type="duplicateValues" dxfId="31" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B795">
+    <cfRule type="duplicateValues" dxfId="30" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B795">
+    <cfRule type="duplicateValues" dxfId="29" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B795">
+    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B796">
+    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B796">
+    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B796">
+    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="23" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B797">
+    <cfRule type="duplicateValues" dxfId="22" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B798">
+    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B798">
+    <cfRule type="duplicateValues" dxfId="20" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B798">
+    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B799">
+    <cfRule type="duplicateValues" dxfId="18" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B799">
+    <cfRule type="duplicateValues" dxfId="17" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B799">
+    <cfRule type="duplicateValues" dxfId="16" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="15" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B800">
+    <cfRule type="duplicateValues" dxfId="13" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B801">
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B801">
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B802">
+    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B802">
+    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B803">
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B803">
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B803">
+    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B804">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B804">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B804">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B806">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Russian Dictionary.xlsx
+++ b/Russian Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="2383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="2546">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -7165,6 +7165,495 @@
   </si>
   <si>
     <t>vay-deeteh pajaluysta</t>
+  </si>
+  <si>
+    <t>he understands Russian well</t>
+  </si>
+  <si>
+    <t>he understands</t>
+  </si>
+  <si>
+    <t>on panimayet</t>
+  </si>
+  <si>
+    <t>он понимает по-русски хорошо</t>
+  </si>
+  <si>
+    <t>on panimayet pa-russki kharasho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">он понимает </t>
+  </si>
+  <si>
+    <t>правда!</t>
+  </si>
+  <si>
+    <t>pravda!</t>
+  </si>
+  <si>
+    <t>Is that true? / Really?</t>
+  </si>
+  <si>
+    <t>what do you have?</t>
+  </si>
+  <si>
+    <t>что у вас есть?</t>
+  </si>
+  <si>
+    <t>chtoh oh vas yest'?</t>
+  </si>
+  <si>
+    <t>I have some milk</t>
+  </si>
+  <si>
+    <t>у меня есть немного молока</t>
+  </si>
+  <si>
+    <t>oh menya yest' nemnoga malakah</t>
+  </si>
+  <si>
+    <t>I have a lot of water</t>
+  </si>
+  <si>
+    <t>у меня много воды</t>
+  </si>
+  <si>
+    <t>oh menya monga vady</t>
+  </si>
+  <si>
+    <t>in Moscow</t>
+  </si>
+  <si>
+    <t>в Москве</t>
+  </si>
+  <si>
+    <t>v mask-veh</t>
+  </si>
+  <si>
+    <t>My husband and I live in Moscow</t>
+  </si>
+  <si>
+    <t>my s mojem jiv-yom v mask-veh</t>
+  </si>
+  <si>
+    <t>мы с мужем живём в Москве</t>
+  </si>
+  <si>
+    <t>you live in Moscow</t>
+  </si>
+  <si>
+    <t>вы живёте в Москве</t>
+  </si>
+  <si>
+    <t>vy jiv-yoh-tieh v mask-veh</t>
+  </si>
+  <si>
+    <t>I don't know where he's</t>
+  </si>
+  <si>
+    <t>я не знаю где он</t>
+  </si>
+  <si>
+    <t>ya ne znayu gdieh on</t>
+  </si>
+  <si>
+    <t>she's not here</t>
+  </si>
+  <si>
+    <t>она не здесь</t>
+  </si>
+  <si>
+    <t>ana né zdes'</t>
+  </si>
+  <si>
+    <t>she's in America</t>
+  </si>
+  <si>
+    <t>она в Америке</t>
+  </si>
+  <si>
+    <t>ana-v Amerikeh</t>
+  </si>
+  <si>
+    <t>we live in America</t>
+  </si>
+  <si>
+    <t>мы живём в Америке</t>
+  </si>
+  <si>
+    <t>my jiv-yom v Amerikeh</t>
+  </si>
+  <si>
+    <t>you live in America</t>
+  </si>
+  <si>
+    <t>вы живёте в Америке</t>
+  </si>
+  <si>
+    <t>vy jiv-yoh-tieh v Amerikeh</t>
+  </si>
+  <si>
+    <t>but I live in Moscow</t>
+  </si>
+  <si>
+    <t>но я живу в Москве</t>
+  </si>
+  <si>
+    <t>no yah ji-voh v mask-veh</t>
+  </si>
+  <si>
+    <t>how many children do you have?</t>
+  </si>
+  <si>
+    <t>сколько у вас детей?</t>
+  </si>
+  <si>
+    <t>we have two boys</t>
+  </si>
+  <si>
+    <t>у нас</t>
+  </si>
+  <si>
+    <t>oh nas</t>
+  </si>
+  <si>
+    <t>we have / at our place</t>
+  </si>
+  <si>
+    <t>two boys</t>
+  </si>
+  <si>
+    <t>два мальчика</t>
+  </si>
+  <si>
+    <t>dvah mal-tchika</t>
+  </si>
+  <si>
+    <t>у нас два мальчика</t>
+  </si>
+  <si>
+    <t>oh nas dvah mal-tchika</t>
+  </si>
+  <si>
+    <t>skolko oh vas dee-tieh?</t>
+  </si>
+  <si>
+    <t>and one girl</t>
+  </si>
+  <si>
+    <t>и одна девочка</t>
+  </si>
+  <si>
+    <t>one girl</t>
+  </si>
+  <si>
+    <t>одна девочка</t>
+  </si>
+  <si>
+    <t>we have one girl</t>
+  </si>
+  <si>
+    <t>у нас одна девочка</t>
+  </si>
+  <si>
+    <t>my husband and I want to drink some milk</t>
+  </si>
+  <si>
+    <t>мы с мужем хотим пить немного молока</t>
+  </si>
+  <si>
+    <t>my s mojem khatim peet' nemnoga malakah</t>
+  </si>
+  <si>
+    <t>we want to drink</t>
+  </si>
+  <si>
+    <t>мы хотим пить</t>
+  </si>
+  <si>
+    <t>my khatim peet'</t>
+  </si>
+  <si>
+    <t>we have no children</t>
+  </si>
+  <si>
+    <t>у нас нет детей</t>
+  </si>
+  <si>
+    <t>oh nas niet dee-tieh</t>
+  </si>
+  <si>
+    <t>we have four girls</t>
+  </si>
+  <si>
+    <t>у нас четыре девочки</t>
+  </si>
+  <si>
+    <t>ee adna dia-vtchka</t>
+  </si>
+  <si>
+    <t>adna dia-vtchka</t>
+  </si>
+  <si>
+    <t>oh nas adna dia-vtchka</t>
+  </si>
+  <si>
+    <t>oh nas tche-terieh dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>do you have four girls?</t>
+  </si>
+  <si>
+    <t>у вас четыре девочки?</t>
+  </si>
+  <si>
+    <t>oh vas tche-terieh dia-vtchkeh?</t>
+  </si>
+  <si>
+    <t>not in America</t>
+  </si>
+  <si>
+    <t>не в Америке</t>
+  </si>
+  <si>
+    <t>né  v Amerikeh</t>
+  </si>
+  <si>
+    <t>but my husband and I</t>
+  </si>
+  <si>
+    <t>но мы с мужем</t>
+  </si>
+  <si>
+    <t>no my s mojem</t>
+  </si>
+  <si>
+    <t>we have four boys</t>
+  </si>
+  <si>
+    <t>у нас четыре мальчика</t>
+  </si>
+  <si>
+    <t>oh nas tche-terieh mal-tchika</t>
+  </si>
+  <si>
+    <t>we have one boy</t>
+  </si>
+  <si>
+    <t>one boy</t>
+  </si>
+  <si>
+    <t>один мальчик</t>
+  </si>
+  <si>
+    <t>adin mal-tchik</t>
+  </si>
+  <si>
+    <t>у нас один мальчик</t>
+  </si>
+  <si>
+    <t>oh nas adin mal-tchik</t>
+  </si>
+  <si>
+    <t>we have one girl and one boy</t>
+  </si>
+  <si>
+    <t>у нас одна девочка и один мальчик</t>
+  </si>
+  <si>
+    <t>oh nas adna dia-vtchka ee adin mal-tchik</t>
+  </si>
+  <si>
+    <t>the boy is big</t>
+  </si>
+  <si>
+    <t>мальчик большой</t>
+  </si>
+  <si>
+    <t>mal-tchik balshoy</t>
+  </si>
+  <si>
+    <t>big (masculin)</t>
+  </si>
+  <si>
+    <t>большой</t>
+  </si>
+  <si>
+    <t>balshoy</t>
+  </si>
+  <si>
+    <t>he's big</t>
+  </si>
+  <si>
+    <t>он большой</t>
+  </si>
+  <si>
+    <t>on balshoy</t>
+  </si>
+  <si>
+    <t>the girl is big</t>
+  </si>
+  <si>
+    <t>девочка большая</t>
+  </si>
+  <si>
+    <t>dia-vtchka balshaya</t>
+  </si>
+  <si>
+    <t>she's big</t>
+  </si>
+  <si>
+    <t>она большая</t>
+  </si>
+  <si>
+    <t>ana balshaya</t>
+  </si>
+  <si>
+    <t>the girl is big and the boy is big</t>
+  </si>
+  <si>
+    <t>девочка большая и мальчик большой</t>
+  </si>
+  <si>
+    <t>dia-vtchka balshaya ee mal-tchik balshoy</t>
+  </si>
+  <si>
+    <t>tell me please, is the boy big?</t>
+  </si>
+  <si>
+    <t>скажите пожалуйста, мальчик большой?</t>
+  </si>
+  <si>
+    <t>skajite pajaluysta, mal-tchik balshoy?</t>
+  </si>
+  <si>
+    <t>is your boy big?</t>
+  </si>
+  <si>
+    <t>ваш мальчик большой?</t>
+  </si>
+  <si>
+    <t>vash mal-tchik balshoy?</t>
+  </si>
+  <si>
+    <t>yes, very big</t>
+  </si>
+  <si>
+    <t>да, очень большой</t>
+  </si>
+  <si>
+    <t>da, ochen' balshoy</t>
+  </si>
+  <si>
+    <t>he's not very big</t>
+  </si>
+  <si>
+    <t>он не очень большой</t>
+  </si>
+  <si>
+    <t>on né ochen balshoy</t>
+  </si>
+  <si>
+    <t>your boy</t>
+  </si>
+  <si>
+    <t>your girl</t>
+  </si>
+  <si>
+    <t>ваш мальчик</t>
+  </si>
+  <si>
+    <t>vash mal-tchik</t>
+  </si>
+  <si>
+    <t>ваша девочка</t>
+  </si>
+  <si>
+    <t>vashah dia-vtchka</t>
+  </si>
+  <si>
+    <t>is your big boy here?</t>
+  </si>
+  <si>
+    <t>ваш большой мальчик здесь?</t>
+  </si>
+  <si>
+    <t>vash balshoy mal-tchik zdes'?</t>
+  </si>
+  <si>
+    <t>is your girl big?</t>
+  </si>
+  <si>
+    <t>ваша девочка большая?</t>
+  </si>
+  <si>
+    <t>vashah dia-vtchka balshaya?</t>
+  </si>
+  <si>
+    <t>she's not very big</t>
+  </si>
+  <si>
+    <t>ana né ochen balshaya</t>
+  </si>
+  <si>
+    <t>она не очень большая</t>
+  </si>
+  <si>
+    <t>but my boy is very big</t>
+  </si>
+  <si>
+    <t>но мой мальчик очень большой</t>
+  </si>
+  <si>
+    <t>no moy mal-tchik ochen balshoy</t>
+  </si>
+  <si>
+    <t>but he's not very big</t>
+  </si>
+  <si>
+    <t>но он не очень большой</t>
+  </si>
+  <si>
+    <t>no on né ochen balshoy</t>
+  </si>
+  <si>
+    <t>правда</t>
+  </si>
+  <si>
+    <t>pravda</t>
+  </si>
+  <si>
+    <t>that's right</t>
+  </si>
+  <si>
+    <t>you are an American, right?</t>
+  </si>
+  <si>
+    <t>vy amerikanets, pravda?</t>
+  </si>
+  <si>
+    <t>вы американец, правда?</t>
+  </si>
+  <si>
+    <t>my husband and I want children</t>
+  </si>
+  <si>
+    <t>мы с мужем хотим детей</t>
+  </si>
+  <si>
+    <t>my s mojem khatim dee-tieh</t>
+  </si>
+  <si>
+    <t>unit 21</t>
+  </si>
+  <si>
+    <t>my girl is big</t>
+  </si>
+  <si>
+    <t>моя девочка большая</t>
+  </si>
+  <si>
+    <t>maya dia-vtchka balshaya</t>
   </si>
 </sst>
 </file>
@@ -7212,7 +7701,1647 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1031">
+  <dxfs count="1195">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -17820,7 +19949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D806"/>
+  <dimension ref="B1:D861"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -26624,3099 +28753,4052 @@
         <v>2375</v>
       </c>
     </row>
+    <row r="807" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B807" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C807" s="1" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="808" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B808" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C808" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="809" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B809" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C809" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D809" s="1" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="810" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B810" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C810" s="1" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="811" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B811" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C811" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="812" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B812" s="1" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C812" s="1" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D812" s="1" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="813" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B813" s="1" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C813" s="1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="814" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B814" s="1" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C814" s="1" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="815" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B815" s="1" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C815" s="1" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="816" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B816" s="1" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C816" s="1" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="817" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B817" s="1" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C817" s="1" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="818" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B818" s="1" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C818" s="1" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="819" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B819" s="1" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C819" s="1" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="820" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B820" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>2424</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="821" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B821" s="1" t="s">
+        <v>2426</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="822" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B822" s="1" t="s">
+        <v>2429</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="823" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B823" s="1" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="824" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B824" s="1" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="825" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B825" s="1" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="826" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B826" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="827" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B827" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="828" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B828" s="1" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>2459</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="829" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B829" s="1" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="830" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B830" s="1" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="831" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B831" s="1" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="832" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B832" s="1" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="833" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B833" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="834" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B834" s="1" t="s">
+        <v>2465</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="835" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B835" s="1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="836" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B836" s="1" t="s">
+        <v>2471</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>2472</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="837" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B837" s="1" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C837" s="1" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="838" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B838" s="1" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="839" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B839" s="1" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="840" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B840" s="1" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="841" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B841" s="1" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="842" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B842" s="1" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="843" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B843" s="1" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="844" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B844" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="845" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B845" s="1" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C845" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="846" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B846" s="1" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="847" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B847" s="1" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="848" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B848" s="1" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="849" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B849" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="850" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B850" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="851" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B851" s="1" t="s">
+        <v>2516</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="852" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B852" s="1" t="s">
+        <v>2519</v>
+      </c>
+      <c r="C852" s="1" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D852" s="1" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="853" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B853" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C853" s="1" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="854" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B854" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="C854" s="1" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D854" s="1" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="855" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B855" s="1" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C855" s="1" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D855" s="1" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="856" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B856" s="1" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C856" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D856" s="1" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="857" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B857" s="1" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C857" s="1" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D857" s="1" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="858" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B858" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C858" s="1" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D858" s="1" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="859" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B859" s="1" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="860" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B860" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="861" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B861" s="1" t="s">
+        <v>2542</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1556"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1555"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1554"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1553"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1552"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1549"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1548"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1547"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1545"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1544"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1543"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1542"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1541"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1537"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1535"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1534"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1532"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1529"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="999" priority="1525"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="998" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="997" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="996" priority="1522"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="995" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="994" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="993" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="992" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="991" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="990" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="989" priority="1515"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="988" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="987" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="986" priority="1512"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="985" priority="1511"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="984" priority="1510"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="983" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="982" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="981" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="980" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="979" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="978" priority="1504"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="977" priority="1503"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="976" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="975" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="974" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="973" priority="1499"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="972" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="971" priority="1497"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="970" priority="1496"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="969" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1651"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="968" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="967" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="966" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="965" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="964" priority="1490"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="963" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="962" priority="1487"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="961" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="960" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="959" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="958" priority="1483"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="957" priority="1482"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="956" priority="1481"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="955" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="954" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="953" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="952" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="951" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="950" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="949" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="948" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="947" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="946" priority="1471"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="945" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="944" priority="1469"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="943" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="942" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="941" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="940" priority="1465"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="939" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="938" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="937" priority="1460"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="936" priority="1459"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="935" priority="1458"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="934" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="933" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="932" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="931" priority="1454"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="930" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="929" priority="1452"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="928" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="927" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="926" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="925" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="924" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="923" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="922" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1601"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="921" priority="1444"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="920" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="919" priority="1442"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="918" priority="1441"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="917" priority="1440"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="916" priority="1439"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="915" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="914" priority="1435"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="913" priority="1434"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="912" priority="1433"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="911" priority="1432"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="910" priority="1431"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="909" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="908" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="907" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="906" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="905" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="904" priority="1423"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="903" priority="1422"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="902" priority="1421"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="901" priority="1420"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="900" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="899" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="898" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="897" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="896" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="895" priority="1412"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="894" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="893" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="892" priority="1407"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="891" priority="1406"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="890" priority="1405"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="889" priority="1404"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="888" priority="1403"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="887" priority="1402"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="886" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="885" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="884" priority="1397"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="883" priority="1396"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="882" priority="1395"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="881" priority="1394"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="880" priority="1393"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="879" priority="1392"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="878" priority="1391"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="877" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="876" priority="1386"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="875" priority="1385"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="874" priority="1384"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="873" priority="1383"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="872" priority="1382"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="871" priority="1381"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="870" priority="1380"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="869" priority="1379"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="868" priority="1376"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="867" priority="1375"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="866" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="865" priority="1371"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="864" priority="1368"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="863" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="862" priority="1364"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="861" priority="1363"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="860" priority="1360"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="859" priority="1359"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="858" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="857" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="856" priority="1352"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="855" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="854" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="853" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="852" priority="1348"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="851" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="850" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="849" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="848" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="847" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="846" priority="1334"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="845" priority="1333"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="844" priority="1332"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="843" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="842" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="841" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="840" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="839" priority="1323"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="838" priority="1322"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="837" priority="1321"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="836" priority="1320"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="835" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="834" priority="1318"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="833" priority="1317"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="832" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="831" priority="1313"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="830" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="829" priority="1311"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="828" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="827" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="826" priority="1302"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="825" priority="1301"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="824" priority="1300"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="823" priority="1299"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="822" priority="1298"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="821" priority="1297"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="820" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="819" priority="1293"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="818" priority="1290"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="817" priority="1289"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="816" priority="1286"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="815" priority="1285"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="814" priority="1284"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="813" priority="1283"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="812" priority="1282"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="811" priority="1281"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="810" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="809" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="808" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="807" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="806" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="805" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="804" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="803" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="802" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="801" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="800" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="799" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="798" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="797" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="796" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="795" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="794" priority="1258"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="793" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="792" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="791" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="790" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="789" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="788" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="787" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="786" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="785" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="784" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="783" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="782" priority="1240"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="781" priority="1239"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="780" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="779" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="778" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="777" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="776" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="775" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="774" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="773" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="772" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="771" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="770" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="769" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="768" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="767" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="766" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="765" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="764" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="763" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="762" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="761" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="760" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="759" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="758" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="757" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="756" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="755" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="754" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="753" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="752" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="751" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="750" priority="1186"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="749" priority="1185"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="748" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="747" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="746" priority="1182"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="745" priority="1181"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="744" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="743" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="742" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="741" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="740" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="739" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="738" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="737" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="736" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="735" priority="1169"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="734" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="733" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="732" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="731" priority="1165"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="730" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="729" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="728" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="727" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="726" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="725" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="724" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="723" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="722" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="721" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="720" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="719" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="718" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="717" priority="1147"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="716" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="715" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="714" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="713" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="712" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="711" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="710" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="709" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="708" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="707" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="706" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="705" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="704" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="703" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="702" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="701" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="700" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="699" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="698" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="697" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="696" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="695" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="694" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="693" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="692" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="691" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="690" priority="1112"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="689" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="688" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="687" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="686" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="685" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="684" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="683" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="682" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="681" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="680" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="679" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="678" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="677" priority="1093"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="676" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="675" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="674" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="673" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="672" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="671" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="670" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="669" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="668" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="667" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="666" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="665" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="664" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="663" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="662" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="661" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="660" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="659" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="658" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="657" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="656" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="655" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="654" priority="1062"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="653" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="652" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="651" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="650" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="649" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="648" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="647" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="646" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="645" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="644" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="643" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="642" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="641" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="640" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="639" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="638" priority="1042"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="637" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="636" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="635" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="634" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="633" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="632" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="631" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="630" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="629" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="628" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="627" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="626" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="625" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="624" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="623" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="622" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="621" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="620" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="619" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="618" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="617" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="616" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="615" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="614" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="613" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="612" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="611" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="1153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="610" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="1152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="609" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="608" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="607" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="606" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="605" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="604" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="603" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="602" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="1132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="601" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="1131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="600" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="599" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="1129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="598" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="1126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="597" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="1125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="596" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="595" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="594" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="593" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="592" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="1120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="591" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="590" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="589" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="588" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="587" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="1113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="586" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="585" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="584" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="583" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="582" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="581" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="580" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="579" priority="943"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="578" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="577" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="576" priority="940"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="575" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="1095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="574" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="1088"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="573" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="1087"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="572" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="571" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="1083"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="570" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="569" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="568" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="1076"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="567" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="1075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="566" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="565" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="564" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="1070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="563" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="562" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="561" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="560" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="1058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="559" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="558" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="557" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="556" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="555" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="554" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="553" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="552" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="551" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="550" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="549" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="548" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="547" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="546" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="545" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="1039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="544" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="1038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="543" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="1037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="542" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="541" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="540" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="539" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="1027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="538" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="537" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="536" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="1022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="535" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="1021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="534" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="1020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="533" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="532" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="531" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="530" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="529" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="1015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="528" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="527" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="1011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="526" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="1010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="525" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="1009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="524" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="523" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="522" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="521" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="520" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="519" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="518" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="517" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="516" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="515" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="514" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="513" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="512" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="511" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="510" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="509" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="508" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="507" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="506" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="505" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="504" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="503" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="502" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="501" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="500" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="499" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="498" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="497" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="496" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="495" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="494" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="493" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="492" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="491" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="490" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="489" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="488" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="940"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="487" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="486" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="939"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="485" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="484" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="483" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="482" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="481" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="480" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="479" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="478" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="477" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="476" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="475" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="474" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="473" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="472" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="471" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="470" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="469" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="468" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="467" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="466" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="465" priority="740"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="464" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="463" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="462" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="461" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="460" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="459" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="458" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="457" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="456" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="455" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="454" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="880"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="453" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="452" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="451" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="450" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="449" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="448" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="447" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="446" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="445" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="444" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="443" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="442" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="441" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="440" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="439" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="438" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="437" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="436" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="435" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="434" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="433" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="432" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="431" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="430" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="429" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="428" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="427" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="426" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="425" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="424" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="423" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="422" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="421" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="420" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="419" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="418" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="417" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="416" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="415" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="414" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="413" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="412" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="411" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="410" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="409" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="408" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="407" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="406" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="405" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="404" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="403" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="402" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="401" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="400" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="399" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="398" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="397" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="396" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="395" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="394" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="393" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="392" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="391" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="390" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="389" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="388" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="387" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="386" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="385" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="384" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="383" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="382" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="381" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="380" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="379" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="378" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="377" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="376" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="375" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="374" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="761"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="373" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="372" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="371" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="370" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="369" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="368" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="367" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="366" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="747"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="365" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="364" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="363" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="746"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="362" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="361" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="360" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="359" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="358" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="357" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="356" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="355" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="354" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="353" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="352" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="351" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="350" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="726"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="349" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="348" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="347" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="346" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="345" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="344" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="343" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="342" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="341" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="340" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="339" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="338" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="337" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="336" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="335" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="334" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="333" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="332" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="331" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="330" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="329" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="328" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="327" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="326" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="325" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="324" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="323" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="322" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="321" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="320" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="319" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="318" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="317" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="316" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="315" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="314" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="313" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="312" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="311" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="310" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="309" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="308" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="307" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="306" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="305" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="304" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="303" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="302" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="301" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="300" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="299" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="298" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="297" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="296" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="295" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="294" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="293" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="292" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="291" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="290" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="289" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="288" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="287" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="286" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="285" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="284" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="283" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="282" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="281" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="280" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="279" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="278" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="277" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="276" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="275" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="274" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="273" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="272" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="271" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="270" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="269" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="268" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="267" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="266" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="265" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="264" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="263" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="262" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="261" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="260" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="259" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="258" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="257" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="256" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="255" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="254" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="253" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="252" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="251" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="250" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="249" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="248" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="247" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="246" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="245" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="244" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="243" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="242" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="241" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="240" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="239" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="238" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="237" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="236" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="235" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="234" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="233" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="232" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="231" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="230" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="229" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="228" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="227" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="226" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="225" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="224" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="223" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="222" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="221" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="220" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="219" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="218" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="217" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="216" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="215" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="214" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="213" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="212" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="211" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="210" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="209" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="208" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="207" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="206" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="205" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="204" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="203" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="202" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="201" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="200" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="199" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="198" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="197" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="196" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="195" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="194" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="193" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="192" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="191" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="190" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="189" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="188" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="187" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="186" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="185" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="184" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="183" priority="307"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
-    <cfRule type="duplicateValues" dxfId="182" priority="1649"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
-    <cfRule type="duplicateValues" dxfId="181" priority="1761"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B807:B1048575">
-    <cfRule type="duplicateValues" dxfId="180" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="463"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
+    <cfRule type="duplicateValues" dxfId="346" priority="1805"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
+    <cfRule type="duplicateValues" dxfId="345" priority="1917"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
+    <cfRule type="duplicateValues" dxfId="344" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="179" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="178" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="177" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="176" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="175" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="174" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="173" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="172" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="171" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="170" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="169" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="168" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="167" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="166" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="165" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="164" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="163" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="162" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="161" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="160" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="159" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="158" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="157" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="156" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="155" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="154" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="153" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="152" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="151" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="150" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="149" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="148" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="147" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="146" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="145" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="144" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="143" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="142" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="141" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="140" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="139" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="138" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="137" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="136" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="135" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="134" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="133" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="132" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="131" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="130" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="129" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="128" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="127" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="126" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="125" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="124" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="123" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="122" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="121" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="120" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="119" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="118" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="117" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="116" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="115" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="114" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="113" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="112" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="111" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="110" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="109" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="108" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="107" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="106" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="105" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="104" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="103" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="102" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="101" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="100" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="99" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="98" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="97" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="96" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="95" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="94" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="93" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="92" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="91" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="90" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="89" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="88" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="87" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="86" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="85" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="84" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="83" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="82" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="81" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="80" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="79" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="78" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="77" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="76" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="75" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="74" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="73" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="72" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="71" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="70" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="69" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="68" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="67" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="66" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="65" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="64" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="63" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="62" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="61" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="60" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="59" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="58" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="57" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="56" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="55" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="54" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="53" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="51" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="50" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="49" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="48" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="47" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="43" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="42" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="41" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="40" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="38" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="37" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="34" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="33" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="31" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="30" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="29" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="23" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="22" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="20" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="18" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="17" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="16" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="15" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="13" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="163" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="162" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B807">
+    <cfRule type="duplicateValues" dxfId="161" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="160" priority="151"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="159" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B809">
+    <cfRule type="duplicateValues" dxfId="158" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B810">
+    <cfRule type="duplicateValues" dxfId="157" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B810">
+    <cfRule type="duplicateValues" dxfId="156" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="155" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="154" priority="140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B812">
+    <cfRule type="duplicateValues" dxfId="153" priority="142"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="152" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="151" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B813">
+    <cfRule type="duplicateValues" dxfId="150" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="149" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="148" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B814">
+    <cfRule type="duplicateValues" dxfId="147" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B815">
+    <cfRule type="duplicateValues" dxfId="146" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B815">
+    <cfRule type="duplicateValues" dxfId="145" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B815">
+    <cfRule type="duplicateValues" dxfId="144" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B816">
+    <cfRule type="duplicateValues" dxfId="143" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B816">
+    <cfRule type="duplicateValues" dxfId="142" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B816">
+    <cfRule type="duplicateValues" dxfId="141" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B817">
+    <cfRule type="duplicateValues" dxfId="140" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B817">
+    <cfRule type="duplicateValues" dxfId="139" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B817">
+    <cfRule type="duplicateValues" dxfId="138" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B818">
+    <cfRule type="duplicateValues" dxfId="137" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B818">
+    <cfRule type="duplicateValues" dxfId="136" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B818">
+    <cfRule type="duplicateValues" dxfId="135" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B819">
+    <cfRule type="duplicateValues" dxfId="134" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B819">
+    <cfRule type="duplicateValues" dxfId="133" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B819">
+    <cfRule type="duplicateValues" dxfId="132" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B820">
+    <cfRule type="duplicateValues" dxfId="131" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B820">
+    <cfRule type="duplicateValues" dxfId="130" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B820">
+    <cfRule type="duplicateValues" dxfId="129" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B821">
+    <cfRule type="duplicateValues" dxfId="128" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B821">
+    <cfRule type="duplicateValues" dxfId="127" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B821">
+    <cfRule type="duplicateValues" dxfId="126" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B822">
+    <cfRule type="duplicateValues" dxfId="125" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B822">
+    <cfRule type="duplicateValues" dxfId="124" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B823">
+    <cfRule type="duplicateValues" dxfId="123" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B823">
+    <cfRule type="duplicateValues" dxfId="122" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B823">
+    <cfRule type="duplicateValues" dxfId="121" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="120" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="119" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B828">
+    <cfRule type="duplicateValues" dxfId="118" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B829">
+    <cfRule type="duplicateValues" dxfId="117" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B829">
+    <cfRule type="duplicateValues" dxfId="116" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B829">
+    <cfRule type="duplicateValues" dxfId="115" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B830">
+    <cfRule type="duplicateValues" dxfId="114" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B830">
+    <cfRule type="duplicateValues" dxfId="113" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B830">
+    <cfRule type="duplicateValues" dxfId="112" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B831">
+    <cfRule type="duplicateValues" dxfId="111" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B831">
+    <cfRule type="duplicateValues" dxfId="110" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B831">
+    <cfRule type="duplicateValues" dxfId="109" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B832">
+    <cfRule type="duplicateValues" dxfId="108" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B832">
+    <cfRule type="duplicateValues" dxfId="107" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B832">
+    <cfRule type="duplicateValues" dxfId="106" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B833">
+    <cfRule type="duplicateValues" dxfId="105" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B833">
+    <cfRule type="duplicateValues" dxfId="104" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B833">
+    <cfRule type="duplicateValues" dxfId="103" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="102" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="101" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B834">
+    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B835">
+    <cfRule type="duplicateValues" dxfId="99" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B835">
+    <cfRule type="duplicateValues" dxfId="98" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B835">
+    <cfRule type="duplicateValues" dxfId="97" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836">
+    <cfRule type="duplicateValues" dxfId="96" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836">
+    <cfRule type="duplicateValues" dxfId="95" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B836">
+    <cfRule type="duplicateValues" dxfId="94" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B837">
+    <cfRule type="duplicateValues" dxfId="93" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B837">
+    <cfRule type="duplicateValues" dxfId="92" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B837">
+    <cfRule type="duplicateValues" dxfId="91" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="90" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="89" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B839">
+    <cfRule type="duplicateValues" dxfId="88" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="87" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="86" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841">
+    <cfRule type="duplicateValues" dxfId="85" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="84" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="83" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844">
+    <cfRule type="duplicateValues" dxfId="82" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B845">
+    <cfRule type="duplicateValues" dxfId="81" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B845">
+    <cfRule type="duplicateValues" dxfId="80" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B845">
+    <cfRule type="duplicateValues" dxfId="79" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B846">
+    <cfRule type="duplicateValues" dxfId="78" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B846">
+    <cfRule type="duplicateValues" dxfId="77" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B846">
+    <cfRule type="duplicateValues" dxfId="76" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="72" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="71" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B848">
+    <cfRule type="duplicateValues" dxfId="70" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B849">
+    <cfRule type="duplicateValues" dxfId="66" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B849">
+    <cfRule type="duplicateValues" dxfId="65" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B849">
+    <cfRule type="duplicateValues" dxfId="64" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="63" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="62" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B851">
+    <cfRule type="duplicateValues" dxfId="61" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B852">
+    <cfRule type="duplicateValues" dxfId="51" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B852">
+    <cfRule type="duplicateValues" dxfId="49" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B852">
+    <cfRule type="duplicateValues" dxfId="47" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B853">
+    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B853">
+    <cfRule type="duplicateValues" dxfId="37" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B853">
+    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B854">
+    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B854">
+    <cfRule type="duplicateValues" dxfId="31" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B854">
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B857">
+    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858">
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B859">
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B859">
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B859">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B861">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Russian Dictionary.xlsx
+++ b/Russian Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="2546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="2649">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -7335,9 +7335,6 @@
     <t>oh nas dvah mal-tchika</t>
   </si>
   <si>
-    <t>skolko oh vas dee-tieh?</t>
-  </si>
-  <si>
     <t>and one girl</t>
   </si>
   <si>
@@ -7380,9 +7377,6 @@
     <t>у нас нет детей</t>
   </si>
   <si>
-    <t>oh nas niet dee-tieh</t>
-  </si>
-  <si>
     <t>we have four girls</t>
   </si>
   <si>
@@ -7641,9 +7635,6 @@
     <t>мы с мужем хотим детей</t>
   </si>
   <si>
-    <t>my s mojem khatim dee-tieh</t>
-  </si>
-  <si>
     <t>unit 21</t>
   </si>
   <si>
@@ -7654,6 +7645,324 @@
   </si>
   <si>
     <t>maya dia-vtchka balshaya</t>
+  </si>
+  <si>
+    <t>ah kto etah s va-mieh?</t>
+  </si>
+  <si>
+    <t>а кто это с вами?</t>
+  </si>
+  <si>
+    <t>and who is this with you?</t>
+  </si>
+  <si>
+    <t>in a store</t>
+  </si>
+  <si>
+    <t>в магазине</t>
+  </si>
+  <si>
+    <t>v magazenieh</t>
+  </si>
+  <si>
+    <t>little girl</t>
+  </si>
+  <si>
+    <t>маленькая девочка</t>
+  </si>
+  <si>
+    <t>malenka dia-vetchka</t>
+  </si>
+  <si>
+    <t>слишком много детей и очень немного денег</t>
+  </si>
+  <si>
+    <t>too many children and very little money</t>
+  </si>
+  <si>
+    <t>you live in America, right?</t>
+  </si>
+  <si>
+    <t>вы живёте в Америке, правда?</t>
+  </si>
+  <si>
+    <t>vy jiv-yoh-tieh v Amerikeh, pravda?</t>
+  </si>
+  <si>
+    <t>в Америке это дорого?</t>
+  </si>
+  <si>
+    <t>v Amerikeh etah doh-raga?</t>
+  </si>
+  <si>
+    <t>in America is it expensive?</t>
+  </si>
+  <si>
+    <t>no, in America it's not very expensive</t>
+  </si>
+  <si>
+    <t>niet, v Amerikeh etah né ochen' doh-raga</t>
+  </si>
+  <si>
+    <t>нет, в Америке это не очень дорого</t>
+  </si>
+  <si>
+    <t>but in Moscow it`s more expensive</t>
+  </si>
+  <si>
+    <t>но в Москве это дороже</t>
+  </si>
+  <si>
+    <t>no v mask-veh etah dah-rojah</t>
+  </si>
+  <si>
+    <t>where's she?</t>
+  </si>
+  <si>
+    <t>где она?</t>
+  </si>
+  <si>
+    <t>gdieh ana?</t>
+  </si>
+  <si>
+    <t>у нас три девочки</t>
+  </si>
+  <si>
+    <t>oh nas tri dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>we have three girls</t>
+  </si>
+  <si>
+    <t>we have no money</t>
+  </si>
+  <si>
+    <t>у нас нет денег</t>
+  </si>
+  <si>
+    <t>oh nas niet dee-nek</t>
+  </si>
+  <si>
+    <t>do you have children?</t>
+  </si>
+  <si>
+    <t>у вас есть дети?</t>
+  </si>
+  <si>
+    <t>oh vas yest' dee-tieh?</t>
+  </si>
+  <si>
+    <t>I have no children</t>
+  </si>
+  <si>
+    <t>у меня нет детей</t>
+  </si>
+  <si>
+    <t>we have no boys</t>
+  </si>
+  <si>
+    <t>no boys</t>
+  </si>
+  <si>
+    <t>нет мальчиков</t>
+  </si>
+  <si>
+    <t>niet mal-tchikov</t>
+  </si>
+  <si>
+    <t>у нас нет мальчиков</t>
+  </si>
+  <si>
+    <t>oh nas niet mal-tchikov</t>
+  </si>
+  <si>
+    <t>we want boys</t>
+  </si>
+  <si>
+    <t>мы хотим мальчиков</t>
+  </si>
+  <si>
+    <t>my khatim mal-tchikov</t>
+  </si>
+  <si>
+    <t>yes, we have children</t>
+  </si>
+  <si>
+    <t>да, у нас есть дети</t>
+  </si>
+  <si>
+    <t>dah, oh nas yest' dee-tieh</t>
+  </si>
+  <si>
+    <t>skolko oh vas dee-tieeeh?</t>
+  </si>
+  <si>
+    <t>oh nas niet dee-tieeeh</t>
+  </si>
+  <si>
+    <t>my s mojem khatim dee-tieeeh</t>
+  </si>
+  <si>
+    <t>slee-shkam mnoga dee-tieeeh ee ochen' nemnoga dee-nek</t>
+  </si>
+  <si>
+    <t>oh menya niet dee-tieeeh</t>
+  </si>
+  <si>
+    <t>we have no girls</t>
+  </si>
+  <si>
+    <t>у нас нет девочек</t>
+  </si>
+  <si>
+    <t>oh nas niet dia-vtchek</t>
+  </si>
+  <si>
+    <t>we want girls</t>
+  </si>
+  <si>
+    <t>мы хотим девочек</t>
+  </si>
+  <si>
+    <t>my khatim dia-vtchek</t>
+  </si>
+  <si>
+    <t>and two girls</t>
+  </si>
+  <si>
+    <t>и две девочки</t>
+  </si>
+  <si>
+    <t>ee dveh dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>I have four girls</t>
+  </si>
+  <si>
+    <t>у меня четыре девочки</t>
+  </si>
+  <si>
+    <t>oh menya tche-terieh dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>they are big</t>
+  </si>
+  <si>
+    <t>они большие</t>
+  </si>
+  <si>
+    <t>they</t>
+  </si>
+  <si>
+    <t xml:space="preserve">они </t>
+  </si>
+  <si>
+    <t>ani</t>
+  </si>
+  <si>
+    <t>they are very big</t>
+  </si>
+  <si>
+    <t>они очень большие</t>
+  </si>
+  <si>
+    <t>and we have only one boy</t>
+  </si>
+  <si>
+    <t>и у нас только один мальчик</t>
+  </si>
+  <si>
+    <t>ee oh nas tol'ka adin mal-tchik</t>
+  </si>
+  <si>
+    <t>ani bal-shieeh</t>
+  </si>
+  <si>
+    <t>ani ochen' bal-shieeh</t>
+  </si>
+  <si>
+    <t>are they big?</t>
+  </si>
+  <si>
+    <t>они большие?</t>
+  </si>
+  <si>
+    <t>ani bal-shieeh?</t>
+  </si>
+  <si>
+    <t>они не здесь</t>
+  </si>
+  <si>
+    <t>ani né zdes'</t>
+  </si>
+  <si>
+    <t>they are not here</t>
+  </si>
+  <si>
+    <t>they are over there in the hotel</t>
+  </si>
+  <si>
+    <t>они там в гостинице</t>
+  </si>
+  <si>
+    <t>ani tam v gastinitseh</t>
+  </si>
+  <si>
+    <t>they are in the hotel</t>
+  </si>
+  <si>
+    <t>они в гостинице</t>
+  </si>
+  <si>
+    <t>ani-v gastinitseh</t>
+  </si>
+  <si>
+    <t>my wife is also there</t>
+  </si>
+  <si>
+    <t>моя жена тоже там</t>
+  </si>
+  <si>
+    <t>maya jenah tojah tam</t>
+  </si>
+  <si>
+    <t>we want to have supper together this evening</t>
+  </si>
+  <si>
+    <t>мы хотим поужинать вместе сегодня вечером</t>
+  </si>
+  <si>
+    <t>my khatim pah-ohji-nat' vmestieh se-vohd-nya ve-tcheram</t>
+  </si>
+  <si>
+    <t>может быть в ресторане интурист</t>
+  </si>
+  <si>
+    <t>mojet byt' v restoraneh inturist</t>
+  </si>
+  <si>
+    <t>maybe in the Intoursit restaurant</t>
+  </si>
+  <si>
+    <t>maybe it's too expensive</t>
+  </si>
+  <si>
+    <t>может быть это слишком дорого</t>
+  </si>
+  <si>
+    <t>mojet byt' etah slee-shkam doh-raga</t>
+  </si>
+  <si>
+    <t>no girls</t>
+  </si>
+  <si>
+    <t>нет девочек</t>
+  </si>
+  <si>
+    <t>niet dia-vtchek</t>
+  </si>
+  <si>
+    <t>unit 22</t>
   </si>
 </sst>
 </file>
@@ -7701,7 +8010,447 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1195">
+  <dxfs count="1239">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -19949,7 +20698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D861"/>
+  <dimension ref="B1:D896"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -27739,7 +28488,7 @@
         <v>2110</v>
       </c>
       <c r="D713" s="1" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="714" spans="2:4" x14ac:dyDescent="0.25">
@@ -27750,7 +28499,7 @@
         <v>2112</v>
       </c>
       <c r="D714" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="715" spans="2:4" x14ac:dyDescent="0.25">
@@ -28923,7 +29672,7 @@
         <v>2429</v>
       </c>
       <c r="C822" s="1" t="s">
-        <v>2439</v>
+        <v>2592</v>
       </c>
       <c r="D822" s="1" t="s">
         <v>2428</v>
@@ -28964,3841 +29713,4490 @@
     </row>
     <row r="826" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B826" s="1" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C826" s="1" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="D826" s="1" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="827" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B827" s="1" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="C827" s="1" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="D827" s="1" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="828" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B828" s="1" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="C828" s="1" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="D828" s="1" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="829" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B829" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C829" s="1" t="s">
         <v>2447</v>
       </c>
-      <c r="C829" s="1" t="s">
-        <v>2448</v>
-      </c>
       <c r="D829" s="1" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="830" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B830" s="1" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C830" s="1" t="s">
         <v>2450</v>
       </c>
-      <c r="C830" s="1" t="s">
-        <v>2451</v>
-      </c>
       <c r="D830" s="1" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="831" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B831" s="1" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="C831" s="1" t="s">
-        <v>2454</v>
+        <v>2593</v>
       </c>
       <c r="D831" s="1" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="832" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B832" s="1" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="C832" s="1" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="D832" s="1" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="833" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B833" s="1" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="C833" s="1" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="D833" s="1" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="834" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B834" s="1" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="C834" s="1" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="D834" s="1" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="835" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B835" s="1" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="C835" s="1" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="D835" s="1" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="836" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B836" s="1" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="C836" s="1" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="D836" s="1" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="837" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B837" s="1" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="C837" s="1" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="D837" s="1" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="838" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B838" s="1" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="C838" s="1" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D838" s="1" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="839" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B839" s="1" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="C839" s="1" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="D839" s="1" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="840" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B840" s="1" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="C840" s="1" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="D840" s="1" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="841" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B841" s="1" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="C841" s="1" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="D841" s="1" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="842" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B842" s="1" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="C842" s="1" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="D842" s="1" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="843" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B843" s="1" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="C843" s="1" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="D843" s="1" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="844" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B844" s="1" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="C844" s="1" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="D844" s="1" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="845" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B845" s="1" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="C845" s="1" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="D845" s="1" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="846" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B846" s="1" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="C846" s="1" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="D846" s="1" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="847" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B847" s="1" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="C847" s="1" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="D847" s="1" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="848" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B848" s="1" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="C848" s="1" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="D848" s="1" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="849" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B849" s="1" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="C849" s="1" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="D849" s="1" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="850" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B850" s="1" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="C850" s="1" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="D850" s="1" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="851" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B851" s="1" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="C851" s="1" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="D851" s="1" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="852" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B852" s="1" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="C852" s="1" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="D852" s="1" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="853" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B853" s="1" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="C853" s="1" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="D853" s="1" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="854" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B854" s="1" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="C854" s="1" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="D854" s="1" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="855" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B855" s="1" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C855" s="1" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="D855" s="1" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="856" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B856" s="1" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C856" s="1" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="D856" s="1" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="857" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B857" s="1" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C857" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D857" s="1" t="s">
         <v>2533</v>
-      </c>
-      <c r="C857" s="1" t="s">
-        <v>2534</v>
-      </c>
-      <c r="D857" s="1" t="s">
-        <v>2535</v>
       </c>
     </row>
     <row r="858" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B858" s="1" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C858" s="1" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="D858" s="1" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="859" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B859" s="1" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="C859" s="1" t="s">
-        <v>2541</v>
+        <v>2594</v>
       </c>
       <c r="D859" s="1" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="860" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B860" s="1" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="C860" s="1" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="D860" s="1" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="861" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B861" s="1" t="s">
-        <v>2542</v>
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="862" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B862" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="863" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B863" s="1" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="864" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B864" s="1" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="865" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B865" s="1" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="866" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B866" s="1" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="867" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B867" s="1" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="868" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B868" s="1" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="869" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B869" s="1" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="870" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B870" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="871" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B871" s="1" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="872" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B872" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="873" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B873" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D873" s="1" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="874" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B874" s="1" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D874" s="1" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="875" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B875" s="1" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D875" s="1" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="876" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B876" s="1" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D876" s="1" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="877" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B877" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D877" s="1" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="878" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B878" s="1" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C878" s="1" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D878" s="1" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="879" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B879" s="1" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C879" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D879" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="880" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B880" s="1" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C880" s="1" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D880" s="1" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="881" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B881" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C881" s="1" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D881" s="1" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="882" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B882" s="1" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C882" s="1" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D882" s="1" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="883" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B883" s="1" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D883" s="1" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="884" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B884" s="1" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C884" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D884" s="1" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="885" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B885" s="1" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C885" s="1" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D885" s="1" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="886" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B886" s="1" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C886" s="1" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D886" s="1" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="887" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B887" s="1" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C887" s="1" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D887" s="1" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="888" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B888" s="1" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D888" s="1" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="889" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B889" s="1" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C889" s="1" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D889" s="1" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="890" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B890" s="1" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C890" s="1" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D890" s="1" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="891" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B891" s="1" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C891" s="1" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D891" s="1" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="892" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B892" s="1" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C892" s="1" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D892" s="1" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="893" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B893" s="1" t="s">
+        <v>2637</v>
+      </c>
+      <c r="C893" s="1" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D893" s="1" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="894" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B894" s="1" t="s">
+        <v>2639</v>
+      </c>
+      <c r="C894" s="1" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D894" s="1" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="895" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B895" s="1" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C895" s="1" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D895" s="1" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="896" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B896" s="1" t="s">
+        <v>2648</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1712"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1711"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1710"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1709"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1708"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1707"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1706"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1705"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1702"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1701"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1699"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1698"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1697"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1696"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1695"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1694"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1693"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1686"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1685"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1684"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1683"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1823"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1682"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1681"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1680"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1679"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1676"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1674"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1667"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1665"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1664"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1663"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1661"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1658"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1654"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1653"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1652"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1651"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1650"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1649"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1646"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1786"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1644"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1643"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1642"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1641"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1640"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1639"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1638"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1637"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1636"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1635"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1634"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1633"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1769"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1628"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1626"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1625"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1624"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1623"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1621"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1761"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1620"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1619"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1616"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1615"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1612"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1611"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1610"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1609"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1747"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1746"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1601"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1600"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1740"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1599"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1080" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1079" priority="1592"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1078" priority="1591"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1590"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1589"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1588"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1587"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1584"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1576"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1569"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1568"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1567"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1057" priority="1566"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1056" priority="1563"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1055" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1561"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1560"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1559"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1558"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1557"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1556"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1553"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1552"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1549"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1548"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1547"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1542"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1541"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1537"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1535"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1532"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1515"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1504"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1503"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1490"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1489"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1487"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1483"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="999" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="998" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="997" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="996" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="995" priority="1469"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="994" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="993" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="992" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="991" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="990" priority="1458"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="989" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="988" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="987" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="986" priority="1454"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="985" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="984" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="983" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="982" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="981" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="980" priority="1442"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="979" priority="1441"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="978" priority="1440"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="977" priority="1439"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="976" priority="1438"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="975" priority="1437"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="974" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="973" priority="1435"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="972" priority="1434"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="971" priority="1433"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="970" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="969" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="968" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="967" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="966" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="965" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="964" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="963" priority="1423"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="962" priority="1422"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="961" priority="1421"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="960" priority="1420"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="959" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="958" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="957" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="956" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="955" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="954" priority="1406"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="953" priority="1405"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="952" priority="1404"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="951" priority="1403"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="950" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="949" priority="1399"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="948" priority="1398"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="947" priority="1397"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="946" priority="1396"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="945" priority="1395"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="944" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="943" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="942" priority="1388"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="941" priority="1387"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="940" priority="1384"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="939" priority="1383"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="938" priority="1380"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="937" priority="1379"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="936" priority="1378"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="935" priority="1377"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="934" priority="1374"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="933" priority="1373"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="932" priority="1370"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="931" priority="1369"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="930" priority="1368"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="929" priority="1367"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="928" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="927" priority="1365"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="926" priority="1360"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="925" priority="1359"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="924" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="923" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="922" priority="1352"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="921" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="920" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="919" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="918" priority="1348"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="917" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="916" priority="1346"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="915" priority="1345"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="914" priority="1342"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="913" priority="1341"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="912" priority="1340"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="911" priority="1339"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="910" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="909" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="908" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="907" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="906" priority="1332"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="905" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="904" priority="1330"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="903" priority="1329"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="902" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="901" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="900" priority="1326"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="899" priority="1325"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="898" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="897" priority="1323"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="896" priority="1322"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="895" priority="1321"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="894" priority="1320"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="893" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="892" priority="1318"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="891" priority="1317"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="890" priority="1316"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="1456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="889" priority="1315"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="888" priority="1314"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="887" priority="1313"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="886" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="885" priority="1311"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="884" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="883" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="882" priority="1304"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="881" priority="1303"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="880" priority="1302"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="879" priority="1301"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="878" priority="1296"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="877" priority="1295"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="876" priority="1292"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="875" priority="1291"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="874" priority="1290"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="873" priority="1289"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="872" priority="1288"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="871" priority="1287"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="870" priority="1286"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="869" priority="1285"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="868" priority="1284"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="867" priority="1283"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="866" priority="1280"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="865" priority="1279"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="864" priority="1278"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="863" priority="1277"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="862" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="861" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="860" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="859" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="858" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="857" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="856" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="855" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="854" priority="1268"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="853" priority="1267"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="852" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="851" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="850" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="849" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="848" priority="1260"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="847" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="846" priority="1256"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="845" priority="1255"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="844" priority="1252"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="843" priority="1251"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="842" priority="1250"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="841" priority="1249"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="840" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="839" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="838" priority="1246"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="837" priority="1245"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="836" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1384"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="835" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1383"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="834" priority="1242"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="833" priority="1241"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="832" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="831" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="830" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="829" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="828" priority="1234"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="827" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="826" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="825" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="824" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="823" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="822" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="821" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="820" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="819" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="818" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="817" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="816" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1354"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="815" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="814" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="813" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="812" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="811" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="810" priority="1208"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="809" priority="1207"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="808" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="807" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="806" priority="1202"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="805" priority="1201"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="804" priority="1200"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="803" priority="1199"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="802" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="801" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="800" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="799" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="798" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="797" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="796" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="795" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="794" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="793" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="792" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1324"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="791" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="790" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="789" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="788" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="787" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="786" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="785" priority="1169"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="784" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="783" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="782" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="781" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="780" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="779" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="778" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="777" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="776" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="775" priority="1153"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="774" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="773" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="772" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="771" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="770" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="769" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="768" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="767" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="766" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="765" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="764" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="763" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="762" priority="1126"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="761" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="760" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="759" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="758" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="757" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="756" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="755" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="754" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="753" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="752" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="751" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="750" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="749" priority="1107"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="748" priority="1106"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="747" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="746" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="745" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="744" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="743" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="742" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="741" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="740" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="739" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="738" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="737" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="736" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="735" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="734" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="733" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="732" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="731" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="1215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="730" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="729" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="728" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="727" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="726" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="725" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="724" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="723" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="1197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="722" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="721" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="720" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="1194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="719" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="1193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="718" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="717" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="1191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="716" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="715" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="714" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="1188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="713" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="1187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="712" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="711" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="1183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="710" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="709" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="708" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="1178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="707" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="1177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="706" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="705" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="1171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="704" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="703" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="702" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="1164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="701" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="1163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="700" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="1162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="699" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="1161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="698" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="697" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="696" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="1158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="695" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="1157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="694" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="1156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="693" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="1155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="692" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="1152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="691" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="1151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="690" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="1150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="689" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="1149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="688" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="1144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="687" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="1143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="686" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="1142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="685" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="1141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="684" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="683" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="682" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="681" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="680" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="679" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="1129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="678" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="677" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="1127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="676" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="675" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="674" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="673" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="672" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="671" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="670" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="1116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="669" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="668" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="667" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="1113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="666" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="1112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="665" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="1111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="664" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="663" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="662" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="661" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="660" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="659" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="658" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="1094"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="657" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="1093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="656" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="655" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="1090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="654" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="653" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="652" priority="940"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="651" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="1078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="650" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="649" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="1077"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="648" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="1076"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="647" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="1066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="646" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="1067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="645" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="644" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="643" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="642" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="641" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="640" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="1054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="639" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="638" priority="912"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="1052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="637" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="636" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="635" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="1048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="634" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="633" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="1046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="632" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="631" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="630" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="629" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="1036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="628" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="1037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="627" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="1034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="626" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="1035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="625" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="624" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="623" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="622" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="1029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="621" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="620" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="619" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="1023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="618" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="1020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="617" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="616" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="615" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="1016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="614" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="613" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="612" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="1015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="611" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="610" priority="873"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="609" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="1010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="608" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="1011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="607" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="606" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="1005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="605" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="604" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="603" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="1000"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="602" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="601" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="600" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="599" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="598" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="597" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="596" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="595" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="594" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="593" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="592" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="591" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="590" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="589" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="588" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="587" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="586" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="585" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="970"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="584" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="583" priority="828"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="582" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="581" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="580" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="579" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="578" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="959"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="577" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="960"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="576" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="575" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="574" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="573" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="572" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="571" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="570" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="569" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="568" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="567" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="566" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="565" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="564" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="563" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="562" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="561" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="560" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="559" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="558" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="557" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="556" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="555" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="554" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="553" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="552" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="921"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="551" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="922"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="550" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="549" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="548" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="547" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="546" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="545" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="544" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="543" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="542" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="541" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="540" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="539" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="538" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="537" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="536" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="535" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="534" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="533" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="532" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="531" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="530" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="887"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="529" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="888"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="528" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="527" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="526" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="525" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="524" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="523" priority="742"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="522" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="521" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="520" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="519" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="518" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="517" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="516" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="515" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="514" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="513" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="512" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="511" priority="724"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="510" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="509" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="508" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="507" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="506" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="505" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="856"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="504" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="503" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="502" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="501" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="500" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="499" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="498" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="497" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="496" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="495" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="494" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="493" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="492" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="491" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="490" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="489" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="488" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="487" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="820"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="486" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="485" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="484" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="483" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="482" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="816"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="481" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="814"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="480" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="815"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="479" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="478" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="477" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="476" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="475" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="474" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="473" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="472" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="471" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="470" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="469" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="468" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="467" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="466" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="465" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="464" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="463" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="462" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="461" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="460" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="459" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="458" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="457" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="456" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="455" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="454" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="453" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="452" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="762"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="451" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="450" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="761"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="449" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="448" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="447" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="446" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="445" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="444" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="443" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="442" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="746"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="441" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="440" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="439" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="438" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="437" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="436" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="435" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="434" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="433" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="730"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="432" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="431" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="430" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="429" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="428" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="427" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="426" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="425" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="424" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="712"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="423" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="422" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="421" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="420" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="419" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="418" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="417" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="416" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="415" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="414" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="413" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="412" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="411" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="410" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="409" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="408" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="407" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="406" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="405" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="404" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="403" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="402" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="401" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="400" priority="548"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="399" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="398" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="397" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="396" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="395" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="394" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="393" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="392" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="391" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="390" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="389" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="388" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="387" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="386" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="385" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="384" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="383" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="382" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="381" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="380" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="379" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="378" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="377" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="376" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="653"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="375" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="374" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="651"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="373" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="372" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="371" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="370" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="369" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="368" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="367" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="366" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="365" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="364" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="363" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="362" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="361" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="360" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="359" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="358" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="357" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="356" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="355" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="354" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="353" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="352" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="351" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="350" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="349" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="348" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="347" priority="463"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
-    <cfRule type="duplicateValues" dxfId="346" priority="1805"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
-    <cfRule type="duplicateValues" dxfId="345" priority="1917"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862:B1048575">
-    <cfRule type="duplicateValues" dxfId="344" priority="2003"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="603"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
+    <cfRule type="duplicateValues" dxfId="390" priority="1945"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
+    <cfRule type="duplicateValues" dxfId="389" priority="2057"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
+    <cfRule type="duplicateValues" dxfId="388" priority="2143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="343" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="342" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="341" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="340" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="339" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="338" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="337" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="336" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="335" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="334" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="333" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="332" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="331" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="330" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="329" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="328" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="327" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="326" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="325" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="324" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="323" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="322" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="321" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="320" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="319" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="318" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="317" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="316" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="315" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="314" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="313" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="312" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="311" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="310" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="309" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="308" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="529"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="307" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="306" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="305" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="304" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="303" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="302" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="301" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="300" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="299" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="298" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="297" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="296" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="295" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="294" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="293" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="292" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="291" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="290" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="289" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="288" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="287" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="286" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="285" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="284" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="283" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="282" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="281" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="280" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="279" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="278" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="277" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="276" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="275" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="274" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="273" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="272" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="271" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="270" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="269" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="268" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="267" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="266" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="265" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="264" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="263" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="262" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="261" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="260" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="259" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="258" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="257" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="256" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="255" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="254" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="253" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="447"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="252" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="251" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="250" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="249" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="248" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="247" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="246" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="245" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="244" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="243" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="242" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="241" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="240" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="239" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="238" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="237" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="236" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="235" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="234" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="233" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="232" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="231" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="230" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="229" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="228" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="227" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="226" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="225" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="224" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="223" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="222" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="221" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="220" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="219" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="218" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="217" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="216" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="215" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="214" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="213" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="212" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="211" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="210" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="209" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="208" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="207" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="206" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="205" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="204" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="203" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="202" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="201" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="200" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="199" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="198" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="197" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="196" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="195" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="193" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="192" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="190" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="189" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="188" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="187" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="186" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="184" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="183" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="182" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="181" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="180" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="179" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="178" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="177" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="176" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="175" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="174" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="173" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="172" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="171" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="309"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="170" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="169" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="168" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="167" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="166" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="165" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="164" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="163" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="162" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="161" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="160" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="159" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="158" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="157" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="156" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="155" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="154" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="153" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="152" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="151" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="150" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="149" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="148" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="147" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="146" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="145" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="144" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="143" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="142" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="141" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="140" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="139" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="138" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="137" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="136" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="135" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="134" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="133" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="132" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="131" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="130" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="129" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="128" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="127" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="126" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="125" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="124" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="123" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="122" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="121" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="120" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="119" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="118" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="117" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="116" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="115" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="114" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="113" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="112" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="111" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="110" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="109" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="108" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="107" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="106" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="105" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="104" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="103" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="102" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="101" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="99" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="98" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="97" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="96" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="95" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="94" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="93" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="92" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="91" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="90" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="89" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="88" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="87" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="86" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="85" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="84" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="83" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="82" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="81" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="80" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="79" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="78" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="77" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="76" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="72" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="71" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="70" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="66" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="65" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="64" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="63" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="62" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="61" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="51" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="49" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="47" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="37" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="31" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="89" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="88" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B863">
+    <cfRule type="duplicateValues" dxfId="87" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="86" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="85" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B868">
+    <cfRule type="duplicateValues" dxfId="84" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="83" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="82" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B866">
+    <cfRule type="duplicateValues" dxfId="81" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="80" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="79" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B867">
+    <cfRule type="duplicateValues" dxfId="78" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="77" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="76" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B869">
+    <cfRule type="duplicateValues" dxfId="75" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B870">
+    <cfRule type="duplicateValues" dxfId="74" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B870">
+    <cfRule type="duplicateValues" dxfId="73" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B870">
+    <cfRule type="duplicateValues" dxfId="72" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B871">
+    <cfRule type="duplicateValues" dxfId="71" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B871">
+    <cfRule type="duplicateValues" dxfId="70" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B871">
+    <cfRule type="duplicateValues" dxfId="69" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="68" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="67" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B873">
+    <cfRule type="duplicateValues" dxfId="66" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B872">
+    <cfRule type="duplicateValues" dxfId="65" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B872">
+    <cfRule type="duplicateValues" dxfId="64" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B872">
+    <cfRule type="duplicateValues" dxfId="63" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="62" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="61" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B874">
+    <cfRule type="duplicateValues" dxfId="60" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B875">
+    <cfRule type="duplicateValues" dxfId="59" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B875">
+    <cfRule type="duplicateValues" dxfId="58" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B875">
+    <cfRule type="duplicateValues" dxfId="57" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="56" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="55" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B877">
+    <cfRule type="duplicateValues" dxfId="54" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="53" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="52" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B879">
+    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="50" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="49" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B881">
+    <cfRule type="duplicateValues" dxfId="48" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="47" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="46" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B882">
+    <cfRule type="duplicateValues" dxfId="45" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="44" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="43" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884">
+    <cfRule type="duplicateValues" dxfId="42" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="41" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="40" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B883">
+    <cfRule type="duplicateValues" dxfId="39" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="38" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="37" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B885">
+    <cfRule type="duplicateValues" dxfId="36" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="34" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886">
+    <cfRule type="duplicateValues" dxfId="33" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="32" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="31" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887">
+    <cfRule type="duplicateValues" dxfId="30" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="29" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="28" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B888">
+    <cfRule type="duplicateValues" dxfId="27" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="26" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889">
+    <cfRule type="duplicateValues" dxfId="24" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="22" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B890">
+    <cfRule type="duplicateValues" dxfId="21" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891">
+    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B892">
+    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893">
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B894">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B895">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B896">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B880">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B880">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B880">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Russian Dictionary.xlsx
+++ b/Russian Dictionary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="2649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="2803">
   <si>
     <t>Word / Expression</t>
   </si>
@@ -7963,6 +7963,468 @@
   </si>
   <si>
     <t>unit 22</t>
+  </si>
+  <si>
+    <t>I can wait</t>
+  </si>
+  <si>
+    <t>вы можете подождать правда?</t>
+  </si>
+  <si>
+    <t>you can wait right?</t>
+  </si>
+  <si>
+    <t>я могу подождать</t>
+  </si>
+  <si>
+    <t>vy mojetieh padahj-dat pravda?</t>
+  </si>
+  <si>
+    <t>ya magu padahj-dat</t>
+  </si>
+  <si>
+    <t>we have some wine</t>
+  </si>
+  <si>
+    <t>у нас есть немного вина</t>
+  </si>
+  <si>
+    <t>oh nas yest' nemnoga vina</t>
+  </si>
+  <si>
+    <t>we have a lot of wine</t>
+  </si>
+  <si>
+    <t>у нас много вина</t>
+  </si>
+  <si>
+    <t>oh nas mnoga vina</t>
+  </si>
+  <si>
+    <t>we want a lot of children</t>
+  </si>
+  <si>
+    <t>мы хотим много детей</t>
+  </si>
+  <si>
+    <t>my khatim mnoga dee-tieeeh</t>
+  </si>
+  <si>
+    <t>we can wait</t>
+  </si>
+  <si>
+    <t>мы можем подождать</t>
+  </si>
+  <si>
+    <t>my mojem padahj-dat</t>
+  </si>
+  <si>
+    <t>can you wait?</t>
+  </si>
+  <si>
+    <t>вы можете подождать?</t>
+  </si>
+  <si>
+    <t>vy mojetieh padahj-dat?</t>
+  </si>
+  <si>
+    <t>we have two girls</t>
+  </si>
+  <si>
+    <t>у нас две девочки</t>
+  </si>
+  <si>
+    <t>oh nas dveh dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>they are now in America</t>
+  </si>
+  <si>
+    <t>они сейчас в Америке</t>
+  </si>
+  <si>
+    <t>ani seetchas v Amerikeh</t>
+  </si>
+  <si>
+    <t>where are they?</t>
+  </si>
+  <si>
+    <t>где они?</t>
+  </si>
+  <si>
+    <t>gdieh ani?</t>
+  </si>
+  <si>
+    <t>the boys are here</t>
+  </si>
+  <si>
+    <t>мальчики здесь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mal-tchikeh zdes' </t>
+  </si>
+  <si>
+    <t>are the boys here?</t>
+  </si>
+  <si>
+    <t>mal-tchikeh zdes'?</t>
+  </si>
+  <si>
+    <t>мальчики здесь?</t>
+  </si>
+  <si>
+    <t>the big boys are here?</t>
+  </si>
+  <si>
+    <t>большие мальчики здесь?</t>
+  </si>
+  <si>
+    <t>bal-shieeh mal-tchikeh zdes'?</t>
+  </si>
+  <si>
+    <t>and the little girl?</t>
+  </si>
+  <si>
+    <t>ee malenka dia-vetchka?</t>
+  </si>
+  <si>
+    <t>и маленькая девочка?</t>
+  </si>
+  <si>
+    <t>the little boy</t>
+  </si>
+  <si>
+    <t>маленький мальчик</t>
+  </si>
+  <si>
+    <t>the boy is little</t>
+  </si>
+  <si>
+    <t>мальчик маленький</t>
+  </si>
+  <si>
+    <t>he's very little</t>
+  </si>
+  <si>
+    <t>он очень маленький</t>
+  </si>
+  <si>
+    <t>our boy</t>
+  </si>
+  <si>
+    <t>наш мальчик</t>
+  </si>
+  <si>
+    <t>nash mal-tchik</t>
+  </si>
+  <si>
+    <t>our boy isn't big</t>
+  </si>
+  <si>
+    <t>nash mal-tchik né balshoy</t>
+  </si>
+  <si>
+    <t>наш мальчик не большой</t>
+  </si>
+  <si>
+    <t>the boys are big</t>
+  </si>
+  <si>
+    <t>мальчики большие</t>
+  </si>
+  <si>
+    <t>mal-tchikeh bal-shieeh</t>
+  </si>
+  <si>
+    <t>but our boy is little</t>
+  </si>
+  <si>
+    <t>но наш мальчик маленький</t>
+  </si>
+  <si>
+    <t>where's your girl?</t>
+  </si>
+  <si>
+    <t>где ваша девочка?</t>
+  </si>
+  <si>
+    <t>gdieh vashah dia-vtchka?</t>
+  </si>
+  <si>
+    <t>our big or little girl?</t>
+  </si>
+  <si>
+    <t>наша большая девочка</t>
+  </si>
+  <si>
+    <t>nasha balshaya eeleeh malenka dia-vetchka?</t>
+  </si>
+  <si>
+    <t>наша большая или маленькая девочка?</t>
+  </si>
+  <si>
+    <t>the big girl wants to speak with me</t>
+  </si>
+  <si>
+    <t>большая девочка хочет говорить со мной</t>
+  </si>
+  <si>
+    <t>balshaya dia-vetchka khotchet gava-reet sam-noy</t>
+  </si>
+  <si>
+    <t>ok, but can you wait?</t>
+  </si>
+  <si>
+    <t>хорошо, но вы можете подождать?</t>
+  </si>
+  <si>
+    <t>kharasho, no vy mojetieh padahj-dat?</t>
+  </si>
+  <si>
+    <t>where's the bathroom?</t>
+  </si>
+  <si>
+    <t>где туалет?</t>
+  </si>
+  <si>
+    <t>gdieh toyalet?</t>
+  </si>
+  <si>
+    <t>the bathroom is over there</t>
+  </si>
+  <si>
+    <t>туалет там</t>
+  </si>
+  <si>
+    <t>toyalet tam</t>
+  </si>
+  <si>
+    <t>yes, they are really over there</t>
+  </si>
+  <si>
+    <t>да, они правда там</t>
+  </si>
+  <si>
+    <t>dah, ani pravda tam</t>
+  </si>
+  <si>
+    <t>our big girl</t>
+  </si>
+  <si>
+    <t>nasha balshaya dia-vetchka</t>
+  </si>
+  <si>
+    <t>your big girl</t>
+  </si>
+  <si>
+    <t>ваша большая девочка</t>
+  </si>
+  <si>
+    <t>vashah balshaya dia-vtchka</t>
+  </si>
+  <si>
+    <t>the little girls</t>
+  </si>
+  <si>
+    <t>маленькие девочки</t>
+  </si>
+  <si>
+    <t>malenkieh dia-vtchkeh</t>
+  </si>
+  <si>
+    <t>where are the little girls?</t>
+  </si>
+  <si>
+    <t>где маленькие девочки?</t>
+  </si>
+  <si>
+    <t>gdieh malenkieh dia-vtchkeh?</t>
+  </si>
+  <si>
+    <t>the family</t>
+  </si>
+  <si>
+    <t>семья</t>
+  </si>
+  <si>
+    <t>semyah</t>
+  </si>
+  <si>
+    <t>one family</t>
+  </si>
+  <si>
+    <t>adna semyah</t>
+  </si>
+  <si>
+    <t>одна семья</t>
+  </si>
+  <si>
+    <t>our family</t>
+  </si>
+  <si>
+    <t>наша семья</t>
+  </si>
+  <si>
+    <t>nasha semyah</t>
+  </si>
+  <si>
+    <t>where's your family?</t>
+  </si>
+  <si>
+    <t>где ваша семья?</t>
+  </si>
+  <si>
+    <t>gdieh vasha semyah?</t>
+  </si>
+  <si>
+    <t>my family?</t>
+  </si>
+  <si>
+    <t>моя семья?</t>
+  </si>
+  <si>
+    <t>maya semyah?</t>
+  </si>
+  <si>
+    <t>the little boys are in America</t>
+  </si>
+  <si>
+    <t>маленькие мальчики в Америке</t>
+  </si>
+  <si>
+    <t>malenkieh mal-tchikeh v Amerikeh</t>
+  </si>
+  <si>
+    <t>but the big girl is here with us</t>
+  </si>
+  <si>
+    <t>вместе с нами</t>
+  </si>
+  <si>
+    <t>vmestieh s-nami</t>
+  </si>
+  <si>
+    <t>но большая девочка здесь вместе с нами</t>
+  </si>
+  <si>
+    <t>no balshaya dia-vetchka zdes' vmestieh s-nami</t>
+  </si>
+  <si>
+    <t>with us / together with us</t>
+  </si>
+  <si>
+    <t>she's here with us</t>
+  </si>
+  <si>
+    <t>она здесь вместе с нами</t>
+  </si>
+  <si>
+    <t>ana zdes' vmestieh s-nami</t>
+  </si>
+  <si>
+    <t>yes, we have a big family</t>
+  </si>
+  <si>
+    <t>да, у нас большая семья</t>
+  </si>
+  <si>
+    <t>dah, oh nas balshaya semyah</t>
+  </si>
+  <si>
+    <t>is that your little boy?</t>
+  </si>
+  <si>
+    <t>это ваш маленький мальчик?</t>
+  </si>
+  <si>
+    <t>malenkey mal-tchik</t>
+  </si>
+  <si>
+    <t>mal-tchik malenkey</t>
+  </si>
+  <si>
+    <t>on ochen' malenkey</t>
+  </si>
+  <si>
+    <t>no nash mal-tchik malenkey</t>
+  </si>
+  <si>
+    <t>etah vash malenkey mal-tchik?</t>
+  </si>
+  <si>
+    <t>this is our little boy</t>
+  </si>
+  <si>
+    <t>etah nash malenkey mal-tchik</t>
+  </si>
+  <si>
+    <t>это наш маленький мальчик</t>
+  </si>
+  <si>
+    <t>how many boys do you have?</t>
+  </si>
+  <si>
+    <t>сколько у вас мальчиков?</t>
+  </si>
+  <si>
+    <t>skolko oh vas mal-tchikov?</t>
+  </si>
+  <si>
+    <t>no, they are little</t>
+  </si>
+  <si>
+    <t>нет, они маленькие</t>
+  </si>
+  <si>
+    <t>niet, ani malenkieh</t>
+  </si>
+  <si>
+    <t>you have a big family</t>
+  </si>
+  <si>
+    <t>у вас большая семья</t>
+  </si>
+  <si>
+    <t>oh vas balshaya semyah</t>
+  </si>
+  <si>
+    <t>we don't have a very big family</t>
+  </si>
+  <si>
+    <t>у нас не очень большая семья</t>
+  </si>
+  <si>
+    <t>oh nas né ochen' balshaya semyah</t>
+  </si>
+  <si>
+    <t>in America families are big</t>
+  </si>
+  <si>
+    <t>в Америке семьи большие</t>
+  </si>
+  <si>
+    <t>v Amerikeh semyieh bal-shieeh</t>
+  </si>
+  <si>
+    <t>many bathrooms</t>
+  </si>
+  <si>
+    <t>много туалетов</t>
+  </si>
+  <si>
+    <t>monga toyaletav</t>
+  </si>
+  <si>
+    <t>he can't wait</t>
+  </si>
+  <si>
+    <t>он не может подождать</t>
+  </si>
+  <si>
+    <t>on né mojet padahj-dat</t>
+  </si>
+  <si>
+    <t>unit 23</t>
   </si>
 </sst>
 </file>
@@ -8010,7 +8472,2567 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1239">
+  <dxfs count="1495">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -20698,7 +23720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D896"/>
+  <dimension ref="B1:D948"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -30480,3723 +33502,4691 @@
         <v>2648</v>
       </c>
     </row>
+    <row r="897" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B897" s="1" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C897" s="1" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D897" s="1" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="898" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B898" s="1" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C898" s="1" t="s">
+        <v>2654</v>
+      </c>
+      <c r="D898" s="1" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="899" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B899" s="1" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C899" s="1" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D899" s="1" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="900" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B900" s="1" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C900" s="1" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D900" s="1" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="901" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B901" s="1" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C901" s="1" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D901" s="1" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="902" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B902" s="1" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C902" s="1" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D902" s="1" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="903" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B903" s="1" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C903" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D903" s="1" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="904" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B904" s="1" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C904" s="1" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D904" s="1" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="905" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B905" s="1" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C905" s="1" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D905" s="1" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="906" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B906" s="1" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C906" s="1" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D906" s="1" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="907" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B907" s="1" t="s">
+        <v>2680</v>
+      </c>
+      <c r="C907" s="1" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D907" s="1" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="908" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B908" s="1" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C908" s="1" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D908" s="1" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="909" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B909" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C909" s="1" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D909" s="1" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="910" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B910" s="1" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C910" s="1" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D910" s="1" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="911" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B911" s="1" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C911" s="1" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D911" s="1" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="912" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B912" s="1" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C912" s="1" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D912" s="1" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="913" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B913" s="1" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C913" s="1" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D913" s="1" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="914" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B914" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C914" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D914" s="1" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="915" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B915" s="1" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C915" s="1" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D915" s="1" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="916" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B916" s="1" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C916" s="1" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D916" s="1" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="917" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B917" s="1" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C917" s="1" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D917" s="1" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="918" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B918" s="1" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C918" s="1" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D918" s="1" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="919" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B919" s="1" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C919" s="1" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D919" s="1" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="920" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B920" s="1" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C920" s="1" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D920" s="1" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="921" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B921" s="1" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C921" s="1" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D921" s="1" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="922" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B922" s="1" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C922" s="1" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D922" s="1" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="923" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B923" s="1" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C923" s="1" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D923" s="1" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="924" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B924" s="1" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C924" s="1" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D924" s="1" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="925" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B925" s="1" t="s">
+        <v>2712</v>
+      </c>
+      <c r="C925" s="1" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D925" s="1" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="926" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B926" s="1" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C926" s="1" t="s">
+        <v>2734</v>
+      </c>
+      <c r="D926" s="1" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="927" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B927" s="1" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C927" s="1" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D927" s="1" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="928" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B928" s="1" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C928" s="1" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D928" s="1" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="929" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B929" s="1" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C929" s="1" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D929" s="1" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="930" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B930" s="1" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C930" s="1" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D930" s="1" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="931" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B931" s="1" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C931" s="1" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D931" s="1" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="932" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B932" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C932" s="1" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D932" s="1" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="933" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B933" s="1" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C933" s="1" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D933" s="1" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="934" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B934" s="1" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C934" s="1" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D934" s="1" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="935" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B935" s="1" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C935" s="1" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D935" s="1" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="936" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B936" s="1" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C936" s="1" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D936" s="1" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="937" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B937" s="1" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C937" s="1" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D937" s="1" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="938" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B938" s="1" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C938" s="1" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D938" s="1" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="939" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B939" s="1" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C939" s="1" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D939" s="1" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="940" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B940" s="1" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C940" s="1" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D940" s="1" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="941" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B941" s="1" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C941" s="1" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D941" s="1" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="942" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B942" s="1" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C942" s="1" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D942" s="1" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="943" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B943" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C943" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D943" s="1" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="944" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B944" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C944" s="1" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D944" s="1" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="945" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B945" s="1" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C945" s="1" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D945" s="1" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="946" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B946" s="1" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C946" s="1" t="s">
+        <v>2798</v>
+      </c>
+      <c r="D946" s="1" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="947" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B947" s="1" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C947" s="1" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D947" s="1" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="948" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B948" s="1" t="s">
+        <v>2802</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="1238" priority="1852"/>
+    <cfRule type="duplicateValues" dxfId="1494" priority="2066"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124">
-    <cfRule type="duplicateValues" dxfId="1237" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="1493" priority="2065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="1236" priority="1850"/>
+    <cfRule type="duplicateValues" dxfId="1492" priority="2064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="1235" priority="1849"/>
+    <cfRule type="duplicateValues" dxfId="1491" priority="2063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="1234" priority="1848"/>
+    <cfRule type="duplicateValues" dxfId="1490" priority="2062"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="1233" priority="1847"/>
+    <cfRule type="duplicateValues" dxfId="1489" priority="2061"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="1232" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="1488" priority="2060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="1231" priority="1845"/>
+    <cfRule type="duplicateValues" dxfId="1487" priority="2059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="1230" priority="1844"/>
+    <cfRule type="duplicateValues" dxfId="1486" priority="2058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="1229" priority="1843"/>
+    <cfRule type="duplicateValues" dxfId="1485" priority="2057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="1228" priority="1842"/>
+    <cfRule type="duplicateValues" dxfId="1484" priority="2056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="1227" priority="1841"/>
+    <cfRule type="duplicateValues" dxfId="1483" priority="2055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="1226" priority="1840"/>
+    <cfRule type="duplicateValues" dxfId="1482" priority="2054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1225" priority="1839"/>
+    <cfRule type="duplicateValues" dxfId="1481" priority="2053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="1224" priority="1838"/>
+    <cfRule type="duplicateValues" dxfId="1480" priority="2052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="1223" priority="1837"/>
+    <cfRule type="duplicateValues" dxfId="1479" priority="2051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="1222" priority="1836"/>
+    <cfRule type="duplicateValues" dxfId="1478" priority="2050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="1221" priority="1835"/>
+    <cfRule type="duplicateValues" dxfId="1477" priority="2049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1220" priority="1834"/>
+    <cfRule type="duplicateValues" dxfId="1476" priority="2048"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="1219" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="1475" priority="2047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="1218" priority="1832"/>
+    <cfRule type="duplicateValues" dxfId="1474" priority="2046"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161">
-    <cfRule type="duplicateValues" dxfId="1217" priority="1831"/>
+    <cfRule type="duplicateValues" dxfId="1473" priority="2045"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162">
-    <cfRule type="duplicateValues" dxfId="1216" priority="1830"/>
+    <cfRule type="duplicateValues" dxfId="1472" priority="2044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163">
-    <cfRule type="duplicateValues" dxfId="1215" priority="1829"/>
+    <cfRule type="duplicateValues" dxfId="1471" priority="2043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B164">
-    <cfRule type="duplicateValues" dxfId="1214" priority="1828"/>
+    <cfRule type="duplicateValues" dxfId="1470" priority="2042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B165">
-    <cfRule type="duplicateValues" dxfId="1213" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="1469" priority="2041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="1212" priority="1826"/>
+    <cfRule type="duplicateValues" dxfId="1468" priority="2040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="1211" priority="1825"/>
+    <cfRule type="duplicateValues" dxfId="1467" priority="2039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="1210" priority="1824"/>
+    <cfRule type="duplicateValues" dxfId="1466" priority="2038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="1209" priority="1823"/>
+    <cfRule type="duplicateValues" dxfId="1465" priority="2037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="duplicateValues" dxfId="1208" priority="1822"/>
+    <cfRule type="duplicateValues" dxfId="1464" priority="2036"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="1207" priority="1821"/>
+    <cfRule type="duplicateValues" dxfId="1463" priority="2035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B176">
-    <cfRule type="duplicateValues" dxfId="1206" priority="1820"/>
+    <cfRule type="duplicateValues" dxfId="1462" priority="2034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="1205" priority="1819"/>
+    <cfRule type="duplicateValues" dxfId="1461" priority="2033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179">
-    <cfRule type="duplicateValues" dxfId="1204" priority="1818"/>
+    <cfRule type="duplicateValues" dxfId="1460" priority="2032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="1203" priority="1817"/>
+    <cfRule type="duplicateValues" dxfId="1459" priority="2031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="1202" priority="1816"/>
+    <cfRule type="duplicateValues" dxfId="1458" priority="2030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="1201" priority="1815"/>
+    <cfRule type="duplicateValues" dxfId="1457" priority="2029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="1200" priority="1814"/>
+    <cfRule type="duplicateValues" dxfId="1456" priority="2028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="1199" priority="1813"/>
+    <cfRule type="duplicateValues" dxfId="1455" priority="2027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="1198" priority="1812"/>
+    <cfRule type="duplicateValues" dxfId="1454" priority="2026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="1197" priority="1811"/>
+    <cfRule type="duplicateValues" dxfId="1453" priority="2025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="1196" priority="1810"/>
+    <cfRule type="duplicateValues" dxfId="1452" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="1195" priority="1809"/>
+    <cfRule type="duplicateValues" dxfId="1451" priority="2023"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="1194" priority="1808"/>
+    <cfRule type="duplicateValues" dxfId="1450" priority="2022"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="1193" priority="1807"/>
+    <cfRule type="duplicateValues" dxfId="1449" priority="2021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1192" priority="1806"/>
+    <cfRule type="duplicateValues" dxfId="1448" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="1191" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="1447" priority="2019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="1190" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="1446" priority="2018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="1189" priority="1803"/>
+    <cfRule type="duplicateValues" dxfId="1445" priority="2017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="1188" priority="1802"/>
+    <cfRule type="duplicateValues" dxfId="1444" priority="2016"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="1187" priority="1801"/>
+    <cfRule type="duplicateValues" dxfId="1443" priority="2015"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B208">
-    <cfRule type="duplicateValues" dxfId="1186" priority="1800"/>
+    <cfRule type="duplicateValues" dxfId="1442" priority="2014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209">
-    <cfRule type="duplicateValues" dxfId="1185" priority="1799"/>
+    <cfRule type="duplicateValues" dxfId="1441" priority="2013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B210">
-    <cfRule type="duplicateValues" dxfId="1184" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1440" priority="2012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B211">
-    <cfRule type="duplicateValues" dxfId="1183" priority="1797"/>
+    <cfRule type="duplicateValues" dxfId="1439" priority="2011"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214">
-    <cfRule type="duplicateValues" dxfId="1182" priority="1796"/>
+    <cfRule type="duplicateValues" dxfId="1438" priority="2010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="1181" priority="1795"/>
+    <cfRule type="duplicateValues" dxfId="1437" priority="2009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B216">
-    <cfRule type="duplicateValues" dxfId="1180" priority="1794"/>
+    <cfRule type="duplicateValues" dxfId="1436" priority="2008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217">
-    <cfRule type="duplicateValues" dxfId="1179" priority="1793"/>
+    <cfRule type="duplicateValues" dxfId="1435" priority="2007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B219">
-    <cfRule type="duplicateValues" dxfId="1178" priority="1792"/>
+    <cfRule type="duplicateValues" dxfId="1434" priority="2006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="1177" priority="1791"/>
+    <cfRule type="duplicateValues" dxfId="1433" priority="2005"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B221">
-    <cfRule type="duplicateValues" dxfId="1176" priority="1790"/>
+    <cfRule type="duplicateValues" dxfId="1432" priority="2004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="1175" priority="1789"/>
+    <cfRule type="duplicateValues" dxfId="1431" priority="2003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B226">
-    <cfRule type="duplicateValues" dxfId="1174" priority="1788"/>
+    <cfRule type="duplicateValues" dxfId="1430" priority="2002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="1173" priority="1787"/>
+    <cfRule type="duplicateValues" dxfId="1429" priority="2001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="1172" priority="1786"/>
+    <cfRule type="duplicateValues" dxfId="1428" priority="2000"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="1171" priority="1784"/>
+    <cfRule type="duplicateValues" dxfId="1427" priority="1998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="1170" priority="1783"/>
+    <cfRule type="duplicateValues" dxfId="1426" priority="1997"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="1169" priority="1782"/>
+    <cfRule type="duplicateValues" dxfId="1425" priority="1996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="1168" priority="1781"/>
+    <cfRule type="duplicateValues" dxfId="1424" priority="1995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1780"/>
+    <cfRule type="duplicateValues" dxfId="1423" priority="1994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="1166" priority="1779"/>
+    <cfRule type="duplicateValues" dxfId="1422" priority="1993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1778"/>
+    <cfRule type="duplicateValues" dxfId="1421" priority="1992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="1164" priority="1777"/>
+    <cfRule type="duplicateValues" dxfId="1420" priority="1991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1776"/>
+    <cfRule type="duplicateValues" dxfId="1419" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="1162" priority="1775"/>
+    <cfRule type="duplicateValues" dxfId="1418" priority="1989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1774"/>
+    <cfRule type="duplicateValues" dxfId="1417" priority="1988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="1160" priority="1773"/>
+    <cfRule type="duplicateValues" dxfId="1416" priority="1987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1772"/>
+    <cfRule type="duplicateValues" dxfId="1415" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="1158" priority="1771"/>
+    <cfRule type="duplicateValues" dxfId="1414" priority="1985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1770"/>
+    <cfRule type="duplicateValues" dxfId="1413" priority="1984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245">
-    <cfRule type="duplicateValues" dxfId="1156" priority="1769"/>
+    <cfRule type="duplicateValues" dxfId="1412" priority="1983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1768"/>
+    <cfRule type="duplicateValues" dxfId="1411" priority="1982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B246">
-    <cfRule type="duplicateValues" dxfId="1154" priority="1767"/>
+    <cfRule type="duplicateValues" dxfId="1410" priority="1981"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1766"/>
+    <cfRule type="duplicateValues" dxfId="1409" priority="1980"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B247">
-    <cfRule type="duplicateValues" dxfId="1152" priority="1765"/>
+    <cfRule type="duplicateValues" dxfId="1408" priority="1979"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1764"/>
+    <cfRule type="duplicateValues" dxfId="1407" priority="1978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="1150" priority="1763"/>
+    <cfRule type="duplicateValues" dxfId="1406" priority="1977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1762"/>
+    <cfRule type="duplicateValues" dxfId="1405" priority="1976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B249">
-    <cfRule type="duplicateValues" dxfId="1148" priority="1761"/>
+    <cfRule type="duplicateValues" dxfId="1404" priority="1975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1760"/>
+    <cfRule type="duplicateValues" dxfId="1403" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="1146" priority="1759"/>
+    <cfRule type="duplicateValues" dxfId="1402" priority="1973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1756"/>
+    <cfRule type="duplicateValues" dxfId="1401" priority="1970"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B252">
-    <cfRule type="duplicateValues" dxfId="1144" priority="1755"/>
+    <cfRule type="duplicateValues" dxfId="1400" priority="1969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1143" priority="1754"/>
+    <cfRule type="duplicateValues" dxfId="1399" priority="1968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="1142" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="1398" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1141" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="1397" priority="1966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1751"/>
+    <cfRule type="duplicateValues" dxfId="1396" priority="1965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1139" priority="1750"/>
+    <cfRule type="duplicateValues" dxfId="1395" priority="1964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B256">
-    <cfRule type="duplicateValues" dxfId="1138" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="1394" priority="1963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1137" priority="1748"/>
+    <cfRule type="duplicateValues" dxfId="1393" priority="1962"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B263">
-    <cfRule type="duplicateValues" dxfId="1136" priority="1747"/>
+    <cfRule type="duplicateValues" dxfId="1392" priority="1961"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1746"/>
+    <cfRule type="duplicateValues" dxfId="1391" priority="1960"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="1134" priority="1745"/>
+    <cfRule type="duplicateValues" dxfId="1390" priority="1959"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1133" priority="1744"/>
+    <cfRule type="duplicateValues" dxfId="1389" priority="1958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="1132" priority="1743"/>
+    <cfRule type="duplicateValues" dxfId="1388" priority="1957"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1131" priority="1742"/>
+    <cfRule type="duplicateValues" dxfId="1387" priority="1956"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B272">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1741"/>
+    <cfRule type="duplicateValues" dxfId="1386" priority="1955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1129" priority="1740"/>
+    <cfRule type="duplicateValues" dxfId="1385" priority="1954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B274">
-    <cfRule type="duplicateValues" dxfId="1128" priority="1739"/>
+    <cfRule type="duplicateValues" dxfId="1384" priority="1953"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1127" priority="1738"/>
+    <cfRule type="duplicateValues" dxfId="1383" priority="1952"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="1126" priority="1737"/>
+    <cfRule type="duplicateValues" dxfId="1382" priority="1951"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1736"/>
+    <cfRule type="duplicateValues" dxfId="1381" priority="1950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B276">
-    <cfRule type="duplicateValues" dxfId="1124" priority="1735"/>
+    <cfRule type="duplicateValues" dxfId="1380" priority="1949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1123" priority="1732"/>
+    <cfRule type="duplicateValues" dxfId="1379" priority="1946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277">
-    <cfRule type="duplicateValues" dxfId="1122" priority="1731"/>
+    <cfRule type="duplicateValues" dxfId="1378" priority="1945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1121" priority="1730"/>
+    <cfRule type="duplicateValues" dxfId="1377" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1729"/>
+    <cfRule type="duplicateValues" dxfId="1376" priority="1943"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1119" priority="1728"/>
+    <cfRule type="duplicateValues" dxfId="1375" priority="1942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="1118" priority="1727"/>
+    <cfRule type="duplicateValues" dxfId="1374" priority="1941"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1117" priority="1724"/>
+    <cfRule type="duplicateValues" dxfId="1373" priority="1938"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="1116" priority="1723"/>
+    <cfRule type="duplicateValues" dxfId="1372" priority="1937"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1722"/>
+    <cfRule type="duplicateValues" dxfId="1371" priority="1936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="1114" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="1370" priority="1935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1113" priority="1720"/>
+    <cfRule type="duplicateValues" dxfId="1369" priority="1934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="1112" priority="1719"/>
+    <cfRule type="duplicateValues" dxfId="1368" priority="1933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1111" priority="1718"/>
+    <cfRule type="duplicateValues" dxfId="1367" priority="1932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1717"/>
+    <cfRule type="duplicateValues" dxfId="1366" priority="1931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1109" priority="1716"/>
+    <cfRule type="duplicateValues" dxfId="1365" priority="1930"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B285">
-    <cfRule type="duplicateValues" dxfId="1108" priority="1715"/>
+    <cfRule type="duplicateValues" dxfId="1364" priority="1929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B286">
-    <cfRule type="duplicateValues" dxfId="1107" priority="1714"/>
+    <cfRule type="duplicateValues" dxfId="1363" priority="1928"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1106" priority="1711"/>
+    <cfRule type="duplicateValues" dxfId="1362" priority="1925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1710"/>
+    <cfRule type="duplicateValues" dxfId="1361" priority="1924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1104" priority="1709"/>
+    <cfRule type="duplicateValues" dxfId="1360" priority="1923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="1103" priority="1708"/>
+    <cfRule type="duplicateValues" dxfId="1359" priority="1922"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1102" priority="1707"/>
+    <cfRule type="duplicateValues" dxfId="1358" priority="1921"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="1101" priority="1706"/>
+    <cfRule type="duplicateValues" dxfId="1357" priority="1920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1703"/>
+    <cfRule type="duplicateValues" dxfId="1356" priority="1917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="1099" priority="1702"/>
+    <cfRule type="duplicateValues" dxfId="1355" priority="1916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1098" priority="1701"/>
+    <cfRule type="duplicateValues" dxfId="1354" priority="1915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="1097" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="1353" priority="1914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1096" priority="1699"/>
+    <cfRule type="duplicateValues" dxfId="1352" priority="1913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1698"/>
+    <cfRule type="duplicateValues" dxfId="1351" priority="1912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1094" priority="1697"/>
+    <cfRule type="duplicateValues" dxfId="1350" priority="1911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="1093" priority="1696"/>
+    <cfRule type="duplicateValues" dxfId="1349" priority="1910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1092" priority="1693"/>
+    <cfRule type="duplicateValues" dxfId="1348" priority="1907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="1091" priority="1692"/>
+    <cfRule type="duplicateValues" dxfId="1347" priority="1906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1691"/>
+    <cfRule type="duplicateValues" dxfId="1346" priority="1905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="1089" priority="1690"/>
+    <cfRule type="duplicateValues" dxfId="1345" priority="1904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1088" priority="1689"/>
+    <cfRule type="duplicateValues" dxfId="1344" priority="1903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="1343" priority="1902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1086" priority="1687"/>
+    <cfRule type="duplicateValues" dxfId="1342" priority="1901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305">
-    <cfRule type="duplicateValues" dxfId="1085" priority="1686"/>
+    <cfRule type="duplicateValues" dxfId="1341" priority="1900"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1682"/>
+    <cfRule type="duplicateValues" dxfId="1340" priority="1896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B308">
-    <cfRule type="duplicateValues" dxfId="1083" priority="1681"/>
+    <cfRule type="duplicateValues" dxfId="1339" priority="1895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1680"/>
+    <cfRule type="duplicateValues" dxfId="1338" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="1081" priority="1679"/>
+    <cfRule type="duplicateValues" dxfId="1337" priority="1893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1080" priority="1678"/>
+    <cfRule type="duplicateValues" dxfId="1336" priority="1892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="1079" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="1335" priority="1891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1078" priority="1676"/>
+    <cfRule type="duplicateValues" dxfId="1334" priority="1890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="1333" priority="1889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1076" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="1332" priority="1886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="1075" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="1331" priority="1885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="1330" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="1073" priority="1667"/>
+    <cfRule type="duplicateValues" dxfId="1329" priority="1881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1072" priority="1664"/>
+    <cfRule type="duplicateValues" dxfId="1328" priority="1878"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="1071" priority="1663"/>
+    <cfRule type="duplicateValues" dxfId="1327" priority="1877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1070" priority="1660"/>
+    <cfRule type="duplicateValues" dxfId="1326" priority="1874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="1069" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="1325" priority="1873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1068" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="1324" priority="1870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="1067" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="1323" priority="1869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1066" priority="1654"/>
+    <cfRule type="duplicateValues" dxfId="1322" priority="1868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="1065" priority="1653"/>
+    <cfRule type="duplicateValues" dxfId="1321" priority="1867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1064" priority="1648"/>
+    <cfRule type="duplicateValues" dxfId="1320" priority="1862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1647"/>
+    <cfRule type="duplicateValues" dxfId="1319" priority="1861"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1062" priority="1646"/>
+    <cfRule type="duplicateValues" dxfId="1318" priority="1860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B320">
-    <cfRule type="duplicateValues" dxfId="1061" priority="1645"/>
+    <cfRule type="duplicateValues" dxfId="1317" priority="1859"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1060" priority="1644"/>
+    <cfRule type="duplicateValues" dxfId="1316" priority="1858"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="1059" priority="1643"/>
+    <cfRule type="duplicateValues" dxfId="1315" priority="1857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="1058" priority="1634"/>
+    <cfRule type="duplicateValues" dxfId="1314" priority="1848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="1057" priority="1633"/>
+    <cfRule type="duplicateValues" dxfId="1313" priority="1847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1056" priority="1632"/>
+    <cfRule type="duplicateValues" dxfId="1312" priority="1846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B326">
-    <cfRule type="duplicateValues" dxfId="1055" priority="1631"/>
+    <cfRule type="duplicateValues" dxfId="1311" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1054" priority="1630"/>
+    <cfRule type="duplicateValues" dxfId="1310" priority="1844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="1053" priority="1629"/>
+    <cfRule type="duplicateValues" dxfId="1309" priority="1843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1052" priority="1628"/>
+    <cfRule type="duplicateValues" dxfId="1308" priority="1842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" dxfId="1051" priority="1627"/>
+    <cfRule type="duplicateValues" dxfId="1307" priority="1841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1050" priority="1624"/>
+    <cfRule type="duplicateValues" dxfId="1306" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="1049" priority="1623"/>
+    <cfRule type="duplicateValues" dxfId="1305" priority="1837"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1620"/>
+    <cfRule type="duplicateValues" dxfId="1304" priority="1834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="1047" priority="1619"/>
+    <cfRule type="duplicateValues" dxfId="1303" priority="1833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1046" priority="1618"/>
+    <cfRule type="duplicateValues" dxfId="1302" priority="1832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="1045" priority="1617"/>
+    <cfRule type="duplicateValues" dxfId="1301" priority="1831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1044" priority="1616"/>
+    <cfRule type="duplicateValues" dxfId="1300" priority="1830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="1043" priority="1615"/>
+    <cfRule type="duplicateValues" dxfId="1299" priority="1829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1042" priority="1614"/>
+    <cfRule type="duplicateValues" dxfId="1298" priority="1828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="1041" priority="1613"/>
+    <cfRule type="duplicateValues" dxfId="1297" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1040" priority="1610"/>
+    <cfRule type="duplicateValues" dxfId="1296" priority="1824"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" dxfId="1039" priority="1609"/>
+    <cfRule type="duplicateValues" dxfId="1295" priority="1823"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1038" priority="1608"/>
+    <cfRule type="duplicateValues" dxfId="1294" priority="1822"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B339">
-    <cfRule type="duplicateValues" dxfId="1037" priority="1607"/>
+    <cfRule type="duplicateValues" dxfId="1293" priority="1821"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1036" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="1292" priority="1818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B342">
-    <cfRule type="duplicateValues" dxfId="1035" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="1291" priority="1817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1034" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="1290" priority="1812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B344">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1289" priority="1811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1032" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="1288" priority="1810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B347">
-    <cfRule type="duplicateValues" dxfId="1031" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="1287" priority="1809"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="1286" priority="1808"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B349">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1593"/>
+    <cfRule type="duplicateValues" dxfId="1285" priority="1807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1028" priority="1590"/>
+    <cfRule type="duplicateValues" dxfId="1284" priority="1804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B350">
-    <cfRule type="duplicateValues" dxfId="1027" priority="1589"/>
+    <cfRule type="duplicateValues" dxfId="1283" priority="1803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1026" priority="1586"/>
+    <cfRule type="duplicateValues" dxfId="1282" priority="1800"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B352">
-    <cfRule type="duplicateValues" dxfId="1025" priority="1585"/>
+    <cfRule type="duplicateValues" dxfId="1281" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1024" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="1280" priority="1796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B353">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="1279" priority="1795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="1278" priority="1794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="1021" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="1277" priority="1793"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1020" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="1276" priority="1792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B355">
-    <cfRule type="duplicateValues" dxfId="1019" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="1275" priority="1791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1018" priority="1576"/>
+    <cfRule type="duplicateValues" dxfId="1274" priority="1790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B356">
-    <cfRule type="duplicateValues" dxfId="1017" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="1273" priority="1789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="1272" priority="1788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B357">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1573"/>
+    <cfRule type="duplicateValues" dxfId="1271" priority="1787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1014" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="1270" priority="1784"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B358">
-    <cfRule type="duplicateValues" dxfId="1013" priority="1569"/>
+    <cfRule type="duplicateValues" dxfId="1269" priority="1783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1012" priority="1568"/>
+    <cfRule type="duplicateValues" dxfId="1268" priority="1782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B359">
-    <cfRule type="duplicateValues" dxfId="1011" priority="1567"/>
+    <cfRule type="duplicateValues" dxfId="1267" priority="1781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1566"/>
+    <cfRule type="duplicateValues" dxfId="1266" priority="1780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B360">
-    <cfRule type="duplicateValues" dxfId="1009" priority="1565"/>
+    <cfRule type="duplicateValues" dxfId="1265" priority="1779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1008" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="1264" priority="1778"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B361">
-    <cfRule type="duplicateValues" dxfId="1007" priority="1563"/>
+    <cfRule type="duplicateValues" dxfId="1263" priority="1777"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="1006" priority="1562"/>
+    <cfRule type="duplicateValues" dxfId="1262" priority="1776"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="1005" priority="1561"/>
+    <cfRule type="duplicateValues" dxfId="1261" priority="1775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1004" priority="1560"/>
+    <cfRule type="duplicateValues" dxfId="1260" priority="1774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B363">
-    <cfRule type="duplicateValues" dxfId="1003" priority="1559"/>
+    <cfRule type="duplicateValues" dxfId="1259" priority="1773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1554"/>
+    <cfRule type="duplicateValues" dxfId="1258" priority="1768"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B365">
-    <cfRule type="duplicateValues" dxfId="1001" priority="1553"/>
+    <cfRule type="duplicateValues" dxfId="1257" priority="1767"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="1000" priority="1550"/>
+    <cfRule type="duplicateValues" dxfId="1256" priority="1764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B366">
-    <cfRule type="duplicateValues" dxfId="999" priority="1549"/>
+    <cfRule type="duplicateValues" dxfId="1255" priority="1763"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="998" priority="1546"/>
+    <cfRule type="duplicateValues" dxfId="1254" priority="1760"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B367">
-    <cfRule type="duplicateValues" dxfId="997" priority="1545"/>
+    <cfRule type="duplicateValues" dxfId="1253" priority="1759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="996" priority="1544"/>
+    <cfRule type="duplicateValues" dxfId="1252" priority="1758"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B368">
-    <cfRule type="duplicateValues" dxfId="995" priority="1543"/>
+    <cfRule type="duplicateValues" dxfId="1251" priority="1757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="994" priority="1540"/>
+    <cfRule type="duplicateValues" dxfId="1250" priority="1754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369">
-    <cfRule type="duplicateValues" dxfId="993" priority="1539"/>
+    <cfRule type="duplicateValues" dxfId="1249" priority="1753"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="992" priority="1538"/>
+    <cfRule type="duplicateValues" dxfId="1248" priority="1752"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370">
-    <cfRule type="duplicateValues" dxfId="991" priority="1537"/>
+    <cfRule type="duplicateValues" dxfId="1247" priority="1751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="990" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="1246" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B371">
-    <cfRule type="duplicateValues" dxfId="989" priority="1535"/>
+    <cfRule type="duplicateValues" dxfId="1245" priority="1749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="988" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="1244" priority="1744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="987" priority="1529"/>
+    <cfRule type="duplicateValues" dxfId="1243" priority="1743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="986" priority="1528"/>
+    <cfRule type="duplicateValues" dxfId="1242" priority="1742"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B375">
-    <cfRule type="duplicateValues" dxfId="985" priority="1527"/>
+    <cfRule type="duplicateValues" dxfId="1241" priority="1741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="984" priority="1524"/>
+    <cfRule type="duplicateValues" dxfId="1240" priority="1738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B376">
-    <cfRule type="duplicateValues" dxfId="983" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="1239" priority="1737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="982" priority="1520"/>
+    <cfRule type="duplicateValues" dxfId="1238" priority="1734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377">
-    <cfRule type="duplicateValues" dxfId="981" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="1237" priority="1733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="980" priority="1518"/>
+    <cfRule type="duplicateValues" dxfId="1236" priority="1732"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381">
-    <cfRule type="duplicateValues" dxfId="979" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="1235" priority="1731"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="978" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="1234" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B382">
-    <cfRule type="duplicateValues" dxfId="977" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="1233" priority="1727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="976" priority="1510"/>
+    <cfRule type="duplicateValues" dxfId="1232" priority="1724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B383">
-    <cfRule type="duplicateValues" dxfId="975" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="1231" priority="1723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="974" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="1230" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B384">
-    <cfRule type="duplicateValues" dxfId="973" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="1229" priority="1721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="972" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="1228" priority="1720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B385">
-    <cfRule type="duplicateValues" dxfId="971" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="1227" priority="1719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="970" priority="1500"/>
+    <cfRule type="duplicateValues" dxfId="1226" priority="1714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B386">
-    <cfRule type="duplicateValues" dxfId="969" priority="1499"/>
+    <cfRule type="duplicateValues" dxfId="1225" priority="1713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="968" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="1224" priority="1708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B387">
-    <cfRule type="duplicateValues" dxfId="967" priority="1493"/>
+    <cfRule type="duplicateValues" dxfId="1223" priority="1707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="966" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="1222" priority="1706"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B388">
-    <cfRule type="duplicateValues" dxfId="965" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="1221" priority="1705"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="964" priority="1490"/>
+    <cfRule type="duplicateValues" dxfId="1220" priority="1704"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="963" priority="1489"/>
+    <cfRule type="duplicateValues" dxfId="1219" priority="1703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="962" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="1218" priority="1702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B392">
-    <cfRule type="duplicateValues" dxfId="961" priority="1487"/>
+    <cfRule type="duplicateValues" dxfId="1217" priority="1701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="960" priority="1486"/>
+    <cfRule type="duplicateValues" dxfId="1216" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="959" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="1215" priority="1699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="958" priority="1482"/>
+    <cfRule type="duplicateValues" dxfId="1214" priority="1696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="957" priority="1481"/>
+    <cfRule type="duplicateValues" dxfId="1213" priority="1695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="956" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="1212" priority="1694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="955" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="1211" priority="1693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="954" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="1210" priority="1692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="953" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="1209" priority="1691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="952" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="1208" priority="1690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B399">
-    <cfRule type="duplicateValues" dxfId="951" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="1207" priority="1689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="950" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="1206" priority="1686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="949" priority="1471"/>
+    <cfRule type="duplicateValues" dxfId="1205" priority="1685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="948" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="1204" priority="1684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B402">
-    <cfRule type="duplicateValues" dxfId="947" priority="1469"/>
+    <cfRule type="duplicateValues" dxfId="1203" priority="1683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="946" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="1202" priority="1682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B403">
-    <cfRule type="duplicateValues" dxfId="945" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="1201" priority="1681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="944" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="1200" priority="1680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="943" priority="1465"/>
+    <cfRule type="duplicateValues" dxfId="1199" priority="1679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="942" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="1198" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="941" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="1197" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="940" priority="1462"/>
+    <cfRule type="duplicateValues" dxfId="1196" priority="1676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B406">
-    <cfRule type="duplicateValues" dxfId="939" priority="1461"/>
+    <cfRule type="duplicateValues" dxfId="1195" priority="1675"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="938" priority="1460"/>
+    <cfRule type="duplicateValues" dxfId="1194" priority="1674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="937" priority="1459"/>
+    <cfRule type="duplicateValues" dxfId="1193" priority="1673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="936" priority="1458"/>
+    <cfRule type="duplicateValues" dxfId="1192" priority="1672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B408">
-    <cfRule type="duplicateValues" dxfId="935" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="1191" priority="1671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="934" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="1670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B409">
-    <cfRule type="duplicateValues" dxfId="933" priority="1455"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="1669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="932" priority="1454"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="1668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B410">
-    <cfRule type="duplicateValues" dxfId="931" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="930" priority="1452"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B411">
-    <cfRule type="duplicateValues" dxfId="929" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="1665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="928" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B412">
-    <cfRule type="duplicateValues" dxfId="927" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="1661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="926" priority="1444"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="1658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B413">
-    <cfRule type="duplicateValues" dxfId="925" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="1657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="924" priority="1442"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B414">
-    <cfRule type="duplicateValues" dxfId="923" priority="1441"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="1655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="922" priority="1436"/>
+    <cfRule type="duplicateValues" dxfId="1178" priority="1650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415">
-    <cfRule type="duplicateValues" dxfId="921" priority="1435"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="1649"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="920" priority="1432"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="1646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416">
-    <cfRule type="duplicateValues" dxfId="919" priority="1431"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="1645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="918" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="1644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B417">
-    <cfRule type="duplicateValues" dxfId="917" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="1643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="916" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="1642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B419">
-    <cfRule type="duplicateValues" dxfId="915" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="1641"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="914" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="1640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B422">
-    <cfRule type="duplicateValues" dxfId="913" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="1639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="912" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="1638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B421">
-    <cfRule type="duplicateValues" dxfId="911" priority="1423"/>
+    <cfRule type="duplicateValues" dxfId="1167" priority="1637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="910" priority="1420"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B423">
-    <cfRule type="duplicateValues" dxfId="909" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="1165" priority="1633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="908" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B424">
-    <cfRule type="duplicateValues" dxfId="907" priority="1417"/>
+    <cfRule type="duplicateValues" dxfId="1163" priority="1631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="906" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B425">
-    <cfRule type="duplicateValues" dxfId="905" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="1161" priority="1629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="904" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B426">
-    <cfRule type="duplicateValues" dxfId="903" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="1159" priority="1627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="902" priority="1412"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B427">
-    <cfRule type="duplicateValues" dxfId="901" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="1157" priority="1625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="900" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428">
-    <cfRule type="duplicateValues" dxfId="899" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="1155" priority="1623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="898" priority="1408"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B429">
-    <cfRule type="duplicateValues" dxfId="897" priority="1407"/>
+    <cfRule type="duplicateValues" dxfId="1153" priority="1621"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="896" priority="1404"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B432">
-    <cfRule type="duplicateValues" dxfId="895" priority="1403"/>
+    <cfRule type="duplicateValues" dxfId="1151" priority="1617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="894" priority="1402"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B431">
-    <cfRule type="duplicateValues" dxfId="893" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="1149" priority="1615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="892" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B434">
-    <cfRule type="duplicateValues" dxfId="891" priority="1399"/>
+    <cfRule type="duplicateValues" dxfId="1147" priority="1613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="890" priority="1396"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B435">
-    <cfRule type="duplicateValues" dxfId="889" priority="1395"/>
+    <cfRule type="duplicateValues" dxfId="1145" priority="1609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="888" priority="1392"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B437">
-    <cfRule type="duplicateValues" dxfId="887" priority="1391"/>
+    <cfRule type="duplicateValues" dxfId="1143" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="886" priority="1390"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B436">
-    <cfRule type="duplicateValues" dxfId="885" priority="1389"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="884" priority="1388"/>
+    <cfRule type="duplicateValues" dxfId="1140" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440">
-    <cfRule type="duplicateValues" dxfId="883" priority="1387"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1601"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="882" priority="1386"/>
+    <cfRule type="duplicateValues" dxfId="1138" priority="1600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441">
-    <cfRule type="duplicateValues" dxfId="881" priority="1385"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="880" priority="1384"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1598"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B443">
-    <cfRule type="duplicateValues" dxfId="879" priority="1383"/>
+    <cfRule type="duplicateValues" dxfId="1135" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="878" priority="1382"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B445">
-    <cfRule type="duplicateValues" dxfId="877" priority="1381"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="876" priority="1378"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B446">
-    <cfRule type="duplicateValues" dxfId="875" priority="1377"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="874" priority="1376"/>
+    <cfRule type="duplicateValues" dxfId="1130" priority="1590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B447">
-    <cfRule type="duplicateValues" dxfId="873" priority="1375"/>
+    <cfRule type="duplicateValues" dxfId="1129" priority="1589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="872" priority="1374"/>
+    <cfRule type="duplicateValues" dxfId="1128" priority="1588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449">
-    <cfRule type="duplicateValues" dxfId="871" priority="1373"/>
+    <cfRule type="duplicateValues" dxfId="1127" priority="1587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="870" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B450">
-    <cfRule type="duplicateValues" dxfId="869" priority="1371"/>
+    <cfRule type="duplicateValues" dxfId="1125" priority="1585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="868" priority="1370"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B452">
-    <cfRule type="duplicateValues" dxfId="867" priority="1369"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="866" priority="1366"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B453">
-    <cfRule type="duplicateValues" dxfId="865" priority="1365"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="864" priority="1360"/>
+    <cfRule type="duplicateValues" dxfId="1120" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B454">
-    <cfRule type="duplicateValues" dxfId="863" priority="1359"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="862" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="1118" priority="1572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B455">
-    <cfRule type="duplicateValues" dxfId="861" priority="1357"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="860" priority="1354"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B457">
-    <cfRule type="duplicateValues" dxfId="859" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="1115" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="858" priority="1352"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B458">
-    <cfRule type="duplicateValues" dxfId="857" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="856" priority="1350"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B460">
-    <cfRule type="duplicateValues" dxfId="855" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="1111" priority="1563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="854" priority="1348"/>
+    <cfRule type="duplicateValues" dxfId="1110" priority="1562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461">
-    <cfRule type="duplicateValues" dxfId="853" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="852" priority="1344"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462">
-    <cfRule type="duplicateValues" dxfId="851" priority="1343"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="850" priority="1342"/>
+    <cfRule type="duplicateValues" dxfId="1106" priority="1556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B464">
-    <cfRule type="duplicateValues" dxfId="849" priority="1341"/>
+    <cfRule type="duplicateValues" dxfId="1105" priority="1555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="848" priority="1340"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465">
-    <cfRule type="duplicateValues" dxfId="847" priority="1339"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="846" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469">
-    <cfRule type="duplicateValues" dxfId="845" priority="1337"/>
+    <cfRule type="duplicateValues" dxfId="1101" priority="1551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="844" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="1100" priority="1550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B470">
-    <cfRule type="duplicateValues" dxfId="843" priority="1335"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="842" priority="1332"/>
+    <cfRule type="duplicateValues" dxfId="1098" priority="1546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B473">
-    <cfRule type="duplicateValues" dxfId="841" priority="1331"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="840" priority="1330"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B474">
-    <cfRule type="duplicateValues" dxfId="839" priority="1329"/>
+    <cfRule type="duplicateValues" dxfId="1095" priority="1543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="838" priority="1328"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B477">
-    <cfRule type="duplicateValues" dxfId="837" priority="1327"/>
+    <cfRule type="duplicateValues" dxfId="1093" priority="1541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="836" priority="1324"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B478">
-    <cfRule type="duplicateValues" dxfId="835" priority="1323"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="834" priority="1320"/>
+    <cfRule type="duplicateValues" dxfId="1090" priority="1534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B479">
-    <cfRule type="duplicateValues" dxfId="833" priority="1319"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="832" priority="1312"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B481">
-    <cfRule type="duplicateValues" dxfId="831" priority="1311"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="830" priority="1310"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B482">
-    <cfRule type="duplicateValues" dxfId="829" priority="1309"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="828" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B484">
-    <cfRule type="duplicateValues" dxfId="827" priority="1307"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="826" priority="1304"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B485">
-    <cfRule type="duplicateValues" dxfId="825" priority="1303"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="824" priority="1300"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B487">
-    <cfRule type="duplicateValues" dxfId="823" priority="1299"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="822" priority="1298"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B486">
-    <cfRule type="duplicateValues" dxfId="821" priority="1297"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="820" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B489">
-    <cfRule type="duplicateValues" dxfId="819" priority="1293"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="818" priority="1292"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490">
-    <cfRule type="duplicateValues" dxfId="817" priority="1291"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="816" priority="1286"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491">
-    <cfRule type="duplicateValues" dxfId="815" priority="1285"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="814" priority="1276"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496">
-    <cfRule type="duplicateValues" dxfId="813" priority="1275"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="812" priority="1274"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497">
-    <cfRule type="duplicateValues" dxfId="811" priority="1273"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="810" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B499">
-    <cfRule type="duplicateValues" dxfId="809" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="808" priority="1270"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B498">
-    <cfRule type="duplicateValues" dxfId="807" priority="1269"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="1483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="806" priority="1266"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="805" priority="1265"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="804" priority="1264"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501">
-    <cfRule type="duplicateValues" dxfId="803" priority="1263"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="802" priority="1262"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B502">
-    <cfRule type="duplicateValues" dxfId="801" priority="1261"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="800" priority="1260"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="799" priority="1259"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="798" priority="1258"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504">
-    <cfRule type="duplicateValues" dxfId="797" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="796" priority="1254"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="795" priority="1253"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="794" priority="1248"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508">
-    <cfRule type="duplicateValues" dxfId="793" priority="1247"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="792" priority="1246"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="1460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="791" priority="1245"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="790" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="789" priority="1243"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="788" priority="1240"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B512">
-    <cfRule type="duplicateValues" dxfId="787" priority="1239"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="786" priority="1238"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B513">
-    <cfRule type="duplicateValues" dxfId="785" priority="1237"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="784" priority="1236"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B515">
-    <cfRule type="duplicateValues" dxfId="783" priority="1235"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="782" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B516">
-    <cfRule type="duplicateValues" dxfId="781" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="780" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B517">
-    <cfRule type="duplicateValues" dxfId="779" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="778" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B518">
-    <cfRule type="duplicateValues" dxfId="777" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="1433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="776" priority="1216"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B522">
-    <cfRule type="duplicateValues" dxfId="775" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="774" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B520">
-    <cfRule type="duplicateValues" dxfId="773" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="772" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B521">
-    <cfRule type="duplicateValues" dxfId="771" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="770" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B523">
-    <cfRule type="duplicateValues" dxfId="769" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="768" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B527">
-    <cfRule type="duplicateValues" dxfId="767" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="766" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526">
-    <cfRule type="duplicateValues" dxfId="765" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="764" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B525">
-    <cfRule type="duplicateValues" dxfId="763" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="762" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B530">
-    <cfRule type="duplicateValues" dxfId="761" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="760" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B536">
-    <cfRule type="duplicateValues" dxfId="759" priority="1189"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="758" priority="1188"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B538">
-    <cfRule type="duplicateValues" dxfId="757" priority="1187"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1401"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="756" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B540">
-    <cfRule type="duplicateValues" dxfId="755" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="754" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B543">
-    <cfRule type="duplicateValues" dxfId="753" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1393"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="752" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B541">
-    <cfRule type="duplicateValues" dxfId="751" priority="1177"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="750" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1386"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B542">
-    <cfRule type="duplicateValues" dxfId="749" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1385"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="748" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1382"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B544">
-    <cfRule type="duplicateValues" dxfId="747" priority="1167"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1381"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="746" priority="1164"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B545">
-    <cfRule type="duplicateValues" dxfId="745" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="744" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B546">
-    <cfRule type="duplicateValues" dxfId="743" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="742" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B548">
-    <cfRule type="duplicateValues" dxfId="741" priority="1159"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="740" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B547">
-    <cfRule type="duplicateValues" dxfId="739" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="738" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B549">
-    <cfRule type="duplicateValues" dxfId="737" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="1369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="736" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="1366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B551">
-    <cfRule type="duplicateValues" dxfId="735" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="1365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="734" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B552">
-    <cfRule type="duplicateValues" dxfId="733" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="1363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="732" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="1358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553">
-    <cfRule type="duplicateValues" dxfId="731" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="730" priority="1142"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554">
-    <cfRule type="duplicateValues" dxfId="729" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="728" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B555">
-    <cfRule type="duplicateValues" dxfId="727" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1349"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="726" priority="1134"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="1348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B556">
-    <cfRule type="duplicateValues" dxfId="725" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="724" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="1344"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B557">
-    <cfRule type="duplicateValues" dxfId="723" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="1343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="722" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B558">
-    <cfRule type="duplicateValues" dxfId="721" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="1341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="720" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="1338"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B559">
-    <cfRule type="duplicateValues" dxfId="719" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="1337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="718" priority="1122"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="1336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B561">
-    <cfRule type="duplicateValues" dxfId="717" priority="1121"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="1335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="716" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="1332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B562">
-    <cfRule type="duplicateValues" dxfId="715" priority="1117"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="1331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="714" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="1330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B564">
-    <cfRule type="duplicateValues" dxfId="713" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="1329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="712" priority="1114"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B563">
-    <cfRule type="duplicateValues" dxfId="711" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="1327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="710" priority="1112"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="1326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B565">
-    <cfRule type="duplicateValues" dxfId="709" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="1325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="708" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="1318"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B566">
-    <cfRule type="duplicateValues" dxfId="707" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="1317"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="706" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B569">
-    <cfRule type="duplicateValues" dxfId="705" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="704" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B567">
-    <cfRule type="duplicateValues" dxfId="703" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="702" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B568">
-    <cfRule type="duplicateValues" dxfId="701" priority="1093"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="700" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570">
-    <cfRule type="duplicateValues" dxfId="699" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1304"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B571">
-    <cfRule type="duplicateValues" dxfId="698" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="697" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B572">
-    <cfRule type="duplicateValues" dxfId="696" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="695" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B575">
-    <cfRule type="duplicateValues" dxfId="694" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="693" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B577">
-    <cfRule type="duplicateValues" dxfId="692" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="691" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B578">
-    <cfRule type="duplicateValues" dxfId="690" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579">
-    <cfRule type="duplicateValues" dxfId="689" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B580">
-    <cfRule type="duplicateValues" dxfId="688" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="687" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="686" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="685" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582">
-    <cfRule type="duplicateValues" dxfId="684" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="683" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B583">
-    <cfRule type="duplicateValues" dxfId="682" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="1266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="681" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="1265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B584">
-    <cfRule type="duplicateValues" dxfId="680" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="1264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="679" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="1262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B587">
-    <cfRule type="duplicateValues" dxfId="678" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="1263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="677" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B586">
-    <cfRule type="duplicateValues" dxfId="676" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="675" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B589">
-    <cfRule type="duplicateValues" dxfId="674" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="673" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B591">
-    <cfRule type="duplicateValues" dxfId="672" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="671" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B592">
-    <cfRule type="duplicateValues" dxfId="670" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="669" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B593">
-    <cfRule type="duplicateValues" dxfId="668" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="667" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B594">
-    <cfRule type="duplicateValues" dxfId="666" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="665" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1238"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B595">
-    <cfRule type="duplicateValues" dxfId="664" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B596">
-    <cfRule type="duplicateValues" dxfId="663" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B601">
-    <cfRule type="duplicateValues" dxfId="662" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="661" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B602">
-    <cfRule type="duplicateValues" dxfId="660" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="659" priority="1016"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="1230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B604">
-    <cfRule type="duplicateValues" dxfId="658" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="1231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="657" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="1228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B603">
-    <cfRule type="duplicateValues" dxfId="656" priority="1015"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="1229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="655" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="1226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B605">
-    <cfRule type="duplicateValues" dxfId="654" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="1227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="653" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B606">
-    <cfRule type="duplicateValues" dxfId="652" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="651" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="1218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B607">
-    <cfRule type="duplicateValues" dxfId="650" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="1219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="649" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="1217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608">
-    <cfRule type="duplicateValues" dxfId="648" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="1216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="647" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="1214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B609">
-    <cfRule type="duplicateValues" dxfId="646" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="1215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="645" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="1208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B610">
-    <cfRule type="duplicateValues" dxfId="644" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="1209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="643" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="1206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611">
-    <cfRule type="duplicateValues" dxfId="642" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="1207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="641" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="1204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B613">
-    <cfRule type="duplicateValues" dxfId="640" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="1205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="639" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="1199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614">
-    <cfRule type="duplicateValues" dxfId="638" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="637" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615">
-    <cfRule type="duplicateValues" dxfId="636" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="1194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="635" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="1191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B616">
-    <cfRule type="duplicateValues" dxfId="634" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="633" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="1188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B617">
-    <cfRule type="duplicateValues" dxfId="632" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="1189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B618">
-    <cfRule type="duplicateValues" dxfId="631" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="1185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="630" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="1183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B619">
-    <cfRule type="duplicateValues" dxfId="629" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="628" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="1181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B620">
-    <cfRule type="duplicateValues" dxfId="627" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="1182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="626" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D621">
-    <cfRule type="duplicateValues" dxfId="625" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="624" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="1175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B621">
-    <cfRule type="duplicateValues" dxfId="623" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="1176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="622" priority="959"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="1173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B625">
-    <cfRule type="duplicateValues" dxfId="621" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="1174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="620" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="1171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B627">
-    <cfRule type="duplicateValues" dxfId="619" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="618" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="1170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B626">
-    <cfRule type="duplicateValues" dxfId="617" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="1169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="616" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B628">
-    <cfRule type="duplicateValues" dxfId="615" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="1167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="614" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="1164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B629">
-    <cfRule type="duplicateValues" dxfId="613" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="1163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="612" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="1160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B630">
-    <cfRule type="duplicateValues" dxfId="611" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="610" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="1156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B631">
-    <cfRule type="duplicateValues" dxfId="609" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="1155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="608" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="1151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632">
-    <cfRule type="duplicateValues" dxfId="607" priority="938"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="1152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="606" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="1147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633">
-    <cfRule type="duplicateValues" dxfId="605" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="1148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="604" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="1143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B634">
-    <cfRule type="duplicateValues" dxfId="603" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="1144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="602" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="1141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B635">
-    <cfRule type="duplicateValues" dxfId="601" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="1142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="600" priority="925"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="1139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B637">
-    <cfRule type="duplicateValues" dxfId="599" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="1140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="598" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="1137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B636">
-    <cfRule type="duplicateValues" dxfId="597" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="1138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="596" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B638">
-    <cfRule type="duplicateValues" dxfId="595" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="1136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="594" priority="919"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B640">
-    <cfRule type="duplicateValues" dxfId="593" priority="920"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="1134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="592" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="1129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B641">
-    <cfRule type="duplicateValues" dxfId="591" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="1130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="590" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="1127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B642">
-    <cfRule type="duplicateValues" dxfId="589" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="588" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="1124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B644">
-    <cfRule type="duplicateValues" dxfId="587" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="1123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="586" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="1121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B643">
-    <cfRule type="duplicateValues" dxfId="585" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="1122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="584" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="1118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645">
-    <cfRule type="duplicateValues" dxfId="583" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="1117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="582" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="1115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646">
-    <cfRule type="duplicateValues" dxfId="581" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="1116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="580" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B647">
-    <cfRule type="duplicateValues" dxfId="579" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="1109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="578" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B648">
-    <cfRule type="duplicateValues" dxfId="577" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="576" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="1104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B649">
-    <cfRule type="duplicateValues" dxfId="575" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="1103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="574" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B650">
-    <cfRule type="duplicateValues" dxfId="573" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="572" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B651">
-    <cfRule type="duplicateValues" dxfId="571" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="1100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="570" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="1097"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B652">
-    <cfRule type="duplicateValues" dxfId="569" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="568" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="1095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B653">
-    <cfRule type="duplicateValues" dxfId="567" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="566" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654">
-    <cfRule type="duplicateValues" dxfId="565" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="1090"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="564" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="1085"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B656">
-    <cfRule type="duplicateValues" dxfId="563" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="1086"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="562" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="1083"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B657">
-    <cfRule type="duplicateValues" dxfId="561" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="1084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="560" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="1081"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B658">
-    <cfRule type="duplicateValues" dxfId="559" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="1082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="558" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B659">
-    <cfRule type="duplicateValues" dxfId="557" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="1079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="556" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="1077"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B660">
-    <cfRule type="duplicateValues" dxfId="555" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="1078"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="554" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="1075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B661">
-    <cfRule type="duplicateValues" dxfId="553" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="1076"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="552" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="1074"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B662">
-    <cfRule type="duplicateValues" dxfId="551" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="550" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="1069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B666">
-    <cfRule type="duplicateValues" dxfId="549" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="1070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="548" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="1067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B667">
-    <cfRule type="duplicateValues" dxfId="547" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="1068"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="546" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="1063"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B668">
-    <cfRule type="duplicateValues" dxfId="545" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="544" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B669">
-    <cfRule type="duplicateValues" dxfId="543" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="542" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="1056"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670">
-    <cfRule type="duplicateValues" dxfId="541" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="1055"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="540" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B672">
-    <cfRule type="duplicateValues" dxfId="539" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="1054"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="538" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="1049"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B673">
-    <cfRule type="duplicateValues" dxfId="537" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="536" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B674">
-    <cfRule type="duplicateValues" dxfId="535" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="534" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="533" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B675">
-    <cfRule type="duplicateValues" dxfId="532" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="1039"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="531" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="1034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="530" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="1035"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B676">
-    <cfRule type="duplicateValues" dxfId="529" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="528" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="527" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677">
-    <cfRule type="duplicateValues" dxfId="526" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="525" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="1028"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="524" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="1029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B678">
-    <cfRule type="duplicateValues" dxfId="523" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="1027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="522" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="521" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="1026"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679">
-    <cfRule type="duplicateValues" dxfId="520" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="519" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="1019"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="518" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="1020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B680">
-    <cfRule type="duplicateValues" dxfId="517" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="516" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1014"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="515" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B681">
-    <cfRule type="duplicateValues" dxfId="514" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1012"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="513" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1008"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="512" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B682">
-    <cfRule type="duplicateValues" dxfId="511" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="1006"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="510" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="509" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="996"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B684">
-    <cfRule type="duplicateValues" dxfId="508" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="994"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="507" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="506" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B685">
-    <cfRule type="duplicateValues" dxfId="505" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="504" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="503" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B687">
-    <cfRule type="duplicateValues" dxfId="502" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="988"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="501" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="500" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B688">
-    <cfRule type="duplicateValues" dxfId="499" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="498" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="497" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B689">
-    <cfRule type="duplicateValues" dxfId="496" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="495" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="494" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B690">
-    <cfRule type="duplicateValues" dxfId="493" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="492" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="491" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="968"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691">
-    <cfRule type="duplicateValues" dxfId="490" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="489" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="488" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="965"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B693">
-    <cfRule type="duplicateValues" dxfId="487" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="486" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="960"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="485" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="959"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B694">
-    <cfRule type="duplicateValues" dxfId="484" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="483" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="951"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="482" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B695">
-    <cfRule type="duplicateValues" dxfId="481" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="480" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="479" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="948"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B696">
-    <cfRule type="duplicateValues" dxfId="478" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="477" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="476" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="945"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B697">
-    <cfRule type="duplicateValues" dxfId="475" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="943"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="474" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="935"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="473" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="936"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B698">
-    <cfRule type="duplicateValues" dxfId="472" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="934"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="471" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="932"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="470" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="933"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B699">
-    <cfRule type="duplicateValues" dxfId="469" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="931"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="468" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="467" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="927"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B701">
-    <cfRule type="duplicateValues" dxfId="466" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="465" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="924"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="464" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="923"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B700">
-    <cfRule type="duplicateValues" dxfId="463" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="922"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="462" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="920"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="461" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="921"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702">
-    <cfRule type="duplicateValues" dxfId="460" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="459" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="458" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B704">
-    <cfRule type="duplicateValues" dxfId="457" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="456" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="455" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="915"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B705">
-    <cfRule type="duplicateValues" dxfId="454" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="453" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="912"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="452" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="911"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B707">
-    <cfRule type="duplicateValues" dxfId="451" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="450" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="449" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="909"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B708">
-    <cfRule type="duplicateValues" dxfId="448" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="447" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="446" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B709">
-    <cfRule type="duplicateValues" dxfId="445" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="904"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="444" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="443" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B711">
-    <cfRule type="duplicateValues" dxfId="442" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="901"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="441" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="440" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B712">
-    <cfRule type="duplicateValues" dxfId="439" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="895"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="438" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="893"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="437" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B713">
-    <cfRule type="duplicateValues" dxfId="436" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="435" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="890"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="434" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="891"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B715">
-    <cfRule type="duplicateValues" dxfId="433" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="432" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="431" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="885"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B716">
-    <cfRule type="duplicateValues" dxfId="430" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="429" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="428" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="875"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B717">
-    <cfRule type="duplicateValues" dxfId="427" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="874"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="426" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="425" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="872"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B718">
-    <cfRule type="duplicateValues" dxfId="424" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="423" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="422" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="869"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720">
-    <cfRule type="duplicateValues" dxfId="421" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="420" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="867"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="419" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B719">
-    <cfRule type="duplicateValues" dxfId="418" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="865"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="417" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="863"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="416" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="864"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B722">
-    <cfRule type="duplicateValues" dxfId="415" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="862"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="414" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="854"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="413" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B724">
-    <cfRule type="duplicateValues" dxfId="412" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="853"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="411" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="410" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B725">
-    <cfRule type="duplicateValues" dxfId="409" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="408" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="842"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="407" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="843"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727">
-    <cfRule type="duplicateValues" dxfId="406" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="841"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="405" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="840"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="404" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="839"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B726">
-    <cfRule type="duplicateValues" dxfId="403" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="402" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="833"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="401" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B728">
-    <cfRule type="duplicateValues" dxfId="400" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="832"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="399" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="831"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="398" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="830"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B730">
-    <cfRule type="duplicateValues" dxfId="397" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="829"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="396" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="395" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="828"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B731">
-    <cfRule type="duplicateValues" dxfId="394" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="826"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="393" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="392" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B732">
-    <cfRule type="duplicateValues" dxfId="391" priority="603"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
-    <cfRule type="duplicateValues" dxfId="390" priority="1945"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
-    <cfRule type="duplicateValues" dxfId="389" priority="2057"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897:B1048576">
-    <cfRule type="duplicateValues" dxfId="388" priority="2143"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="817"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B44 D45 B46:B101 B103:B106 B108:B123 B125:B126 B131:B132 B134 B137 B143:B147 B150:B152 B158:B160 D154 B168:B169 B172 B175 B178 B180:B185 B188 B190 B199 D195 B203 B212:B213 B218 B222:B224 B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576">
+    <cfRule type="duplicateValues" dxfId="646" priority="2159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B573:B574 B505 B1:B229 B231:B232 B235 B239:B240 B242:B244 B251 B254 B257:B262 B264:B269 B273 B278 B288:B289 B291 B295:B299 B306:B307 B314 B322:B324 B331 B333 B337:B338 B340:B341 B343 B348 B345:B346 B351 B364 B372:B373 B378:B380 B389:B390 B396:B397 B401 B418 B420 B430 B433 B438:B439 B442 B444 B448 B451 B456 B459 B463 B466:B468 B471:B472 B475:B476 B480 B483 B488 B492:B495 B507 B511 B514 B519 B524 B528:B529 B531:B535 B537 B539 B550 B560 B576 B585 B588 B590 B597:B600 B612 B622:B624 B639 B655 B663:B665 B671 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576">
+    <cfRule type="duplicateValues" dxfId="645" priority="2271"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B683 B1:B674 B686 B692 B703 B706 B710 B714 B721 B723 B729 B739 B755 B758 B766 B768:B769 B775:B776 B781:B783 B805 B808 B811 B824:B827 B838 B840 B842:B843 B847 B850 B855:B856 B860 B862 B864:B865 B876 B878 B897 B911 B927:B928 B930 B932:B933 B942 B950:B1048576">
+    <cfRule type="duplicateValues" dxfId="644" priority="2357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="387" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="811"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="386" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="812"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B733">
-    <cfRule type="duplicateValues" dxfId="385" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="813"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="384" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="806"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="383" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="805"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B734">
-    <cfRule type="duplicateValues" dxfId="382" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="807"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="381" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="802"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="380" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="803"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B735">
-    <cfRule type="duplicateValues" dxfId="379" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="804"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="378" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="377" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="798"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B736">
-    <cfRule type="duplicateValues" dxfId="376" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="796"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="375" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="790"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="374" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="791"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737">
-    <cfRule type="duplicateValues" dxfId="373" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="792"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="372" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="788"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="371" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="789"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738">
-    <cfRule type="duplicateValues" dxfId="370" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="369" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="782"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B740">
-    <cfRule type="duplicateValues" dxfId="368" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="367" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="780"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="366" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B741">
-    <cfRule type="duplicateValues" dxfId="365" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="781"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="364" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="773"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="363" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="774"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B742">
-    <cfRule type="duplicateValues" dxfId="362" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="361" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="360" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="771"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B743">
-    <cfRule type="duplicateValues" dxfId="359" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="358" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="764"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="357" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B744">
-    <cfRule type="duplicateValues" dxfId="356" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="355" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="749"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="354" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B745">
-    <cfRule type="duplicateValues" dxfId="353" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="751"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="352" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="743"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="351" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="744"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B746">
-    <cfRule type="duplicateValues" dxfId="350" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="745"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="349" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="737"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="348" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747">
-    <cfRule type="duplicateValues" dxfId="347" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="739"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="346" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="735"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="345" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="736"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B748">
-    <cfRule type="duplicateValues" dxfId="344" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="343" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="342" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="726"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B749">
-    <cfRule type="duplicateValues" dxfId="341" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="340" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="339" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="716"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B750">
-    <cfRule type="duplicateValues" dxfId="338" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="718"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="337" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="714"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="336" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="713"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B751">
-    <cfRule type="duplicateValues" dxfId="335" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="334" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="333" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B752">
-    <cfRule type="duplicateValues" dxfId="332" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="707"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="331" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="701"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="330" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B753">
-    <cfRule type="duplicateValues" dxfId="329" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="328" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="327" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="699"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B754">
-    <cfRule type="duplicateValues" dxfId="326" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="325" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="695"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="324" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="696"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B756">
-    <cfRule type="duplicateValues" dxfId="323" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="697"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="322" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="692"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="321" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757">
-    <cfRule type="duplicateValues" dxfId="320" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="319" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="318" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B759">
-    <cfRule type="duplicateValues" dxfId="317" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="316" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="315" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="687"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B760">
-    <cfRule type="duplicateValues" dxfId="314" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="313" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="683"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="312" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B761">
-    <cfRule type="duplicateValues" dxfId="311" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="685"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="310" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="309" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B764">
-    <cfRule type="duplicateValues" dxfId="308" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="307" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B762">
-    <cfRule type="duplicateValues" dxfId="306" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="305" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B763">
-    <cfRule type="duplicateValues" dxfId="304" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="674"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="303" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="302" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="669"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B765">
-    <cfRule type="duplicateValues" dxfId="301" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="300" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="299" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="665"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B767">
-    <cfRule type="duplicateValues" dxfId="298" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="297" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="661"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="296" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B770">
-    <cfRule type="duplicateValues" dxfId="295" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="663"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="294" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="293" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="659"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B771">
-    <cfRule type="duplicateValues" dxfId="292" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="291" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="655"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="290" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B772">
-    <cfRule type="duplicateValues" dxfId="289" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="657"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="288" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="643"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="287" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B773">
-    <cfRule type="duplicateValues" dxfId="286" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="285" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B774">
-    <cfRule type="duplicateValues" dxfId="284" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="283" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="282" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B777">
-    <cfRule type="duplicateValues" dxfId="281" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="280" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="279" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B778">
-    <cfRule type="duplicateValues" dxfId="278" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="277" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="276" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B779">
-    <cfRule type="duplicateValues" dxfId="275" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="274" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="273" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B780">
-    <cfRule type="duplicateValues" dxfId="272" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="271" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="270" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="609"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784">
-    <cfRule type="duplicateValues" dxfId="269" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="268" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="267" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B785">
-    <cfRule type="duplicateValues" dxfId="266" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="265" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="264" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B786">
-    <cfRule type="duplicateValues" dxfId="263" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="601"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="262" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="261" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B787">
-    <cfRule type="duplicateValues" dxfId="260" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="259" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="258" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B788">
-    <cfRule type="duplicateValues" dxfId="257" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="256" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="255" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B789">
-    <cfRule type="duplicateValues" dxfId="254" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="253" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="252" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B790">
-    <cfRule type="duplicateValues" dxfId="251" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="250" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="249" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B791">
-    <cfRule type="duplicateValues" dxfId="248" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="247" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="246" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B792">
-    <cfRule type="duplicateValues" dxfId="245" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="244" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="243" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B793">
-    <cfRule type="duplicateValues" dxfId="242" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="241" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="240" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794">
-    <cfRule type="duplicateValues" dxfId="239" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="238" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="557"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="237" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B795">
-    <cfRule type="duplicateValues" dxfId="236" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="235" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="234" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="555"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B796">
-    <cfRule type="duplicateValues" dxfId="233" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="232" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="231" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B797">
-    <cfRule type="duplicateValues" dxfId="230" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="229" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="228" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B798">
-    <cfRule type="duplicateValues" dxfId="227" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="226" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="225" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B799">
-    <cfRule type="duplicateValues" dxfId="224" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="223" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="222" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B800">
-    <cfRule type="duplicateValues" dxfId="221" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="541"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="220" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B801">
-    <cfRule type="duplicateValues" dxfId="219" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="218" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B802">
-    <cfRule type="duplicateValues" dxfId="217" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="216" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="215" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="523"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B803">
-    <cfRule type="duplicateValues" dxfId="214" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="213" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="212" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804">
-    <cfRule type="duplicateValues" dxfId="211" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="210" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="209" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B806">
-    <cfRule type="duplicateValues" dxfId="208" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="207" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="206" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B807">
-    <cfRule type="duplicateValues" dxfId="205" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="204" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="203" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B809">
-    <cfRule type="duplicateValues" dxfId="202" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="201" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B810">
-    <cfRule type="duplicateValues" dxfId="200" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="199" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="198" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B812">
-    <cfRule type="duplicateValues" dxfId="197" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="196" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="195" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B813">
-    <cfRule type="duplicateValues" dxfId="194" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="193" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="192" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B814">
-    <cfRule type="duplicateValues" dxfId="191" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="190" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="189" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B815">
-    <cfRule type="duplicateValues" dxfId="188" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="187" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="186" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B816">
-    <cfRule type="duplicateValues" dxfId="185" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="184" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="183" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B817">
-    <cfRule type="duplicateValues" dxfId="182" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="181" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="180" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B818">
-    <cfRule type="duplicateValues" dxfId="179" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="178" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="177" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B819">
-    <cfRule type="duplicateValues" dxfId="176" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="469"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="175" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="174" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B820">
-    <cfRule type="duplicateValues" dxfId="173" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="172" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="461"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="171" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B821">
-    <cfRule type="duplicateValues" dxfId="170" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="463"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="169" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="459"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B822">
-    <cfRule type="duplicateValues" dxfId="168" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="167" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="166" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B823">
-    <cfRule type="duplicateValues" dxfId="165" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="164" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="163" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B828">
-    <cfRule type="duplicateValues" dxfId="162" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="161" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="444"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="160" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="445"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829">
-    <cfRule type="duplicateValues" dxfId="159" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="158" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="157" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830">
-    <cfRule type="duplicateValues" dxfId="156" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="155" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="154" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="439"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B831">
-    <cfRule type="duplicateValues" dxfId="153" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="440"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="152" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="151" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="436"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B832">
-    <cfRule type="duplicateValues" dxfId="150" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="149" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="148" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B833">
-    <cfRule type="duplicateValues" dxfId="147" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="146" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="145" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B834">
-    <cfRule type="duplicateValues" dxfId="144" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="143" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="142" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B835">
-    <cfRule type="duplicateValues" dxfId="141" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="140" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="139" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B836">
-    <cfRule type="duplicateValues" dxfId="138" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="137" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="136" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B837">
-    <cfRule type="duplicateValues" dxfId="135" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="134" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="133" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B839">
-    <cfRule type="duplicateValues" dxfId="132" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="131" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="130" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B841">
-    <cfRule type="duplicateValues" dxfId="129" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="128" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="127" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B844">
-    <cfRule type="duplicateValues" dxfId="126" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="125" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="124" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B845">
-    <cfRule type="duplicateValues" dxfId="123" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="122" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="121" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B846">
-    <cfRule type="duplicateValues" dxfId="120" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="119" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="396"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="118" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B848">
-    <cfRule type="duplicateValues" dxfId="117" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="398"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="116" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="115" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B849">
-    <cfRule type="duplicateValues" dxfId="114" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="392"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="113" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="112" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B851">
-    <cfRule type="duplicateValues" dxfId="111" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="389"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="110" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="109" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B852">
-    <cfRule type="duplicateValues" dxfId="108" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="107" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="106" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B853">
-    <cfRule type="duplicateValues" dxfId="105" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="374"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="103" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="370"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B854">
-    <cfRule type="duplicateValues" dxfId="102" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="371"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="101" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="100" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B857">
-    <cfRule type="duplicateValues" dxfId="99" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="368"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="98" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="363"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="97" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B858">
-    <cfRule type="duplicateValues" dxfId="96" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="95" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="360"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="94" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="361"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B859">
-    <cfRule type="duplicateValues" dxfId="93" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="92" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="357"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="91" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B861">
-    <cfRule type="duplicateValues" dxfId="90" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="355"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="89" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="88" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B863">
-    <cfRule type="duplicateValues" dxfId="87" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="348"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="86" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="85" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B868">
-    <cfRule type="duplicateValues" dxfId="84" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="83" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="82" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B866">
-    <cfRule type="duplicateValues" dxfId="81" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="80" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="79" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B867">
-    <cfRule type="duplicateValues" dxfId="78" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="77" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="76" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B869">
-    <cfRule type="duplicateValues" dxfId="75" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="74" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="320"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="73" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B870">
-    <cfRule type="duplicateValues" dxfId="72" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="322"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="71" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="70" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="315"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B871">
-    <cfRule type="duplicateValues" dxfId="69" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="68" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="311"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="67" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B873">
-    <cfRule type="duplicateValues" dxfId="66" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="313"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="65" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="305"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="64" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="306"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B872">
-    <cfRule type="duplicateValues" dxfId="63" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="62" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="61" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B874">
-    <cfRule type="duplicateValues" dxfId="60" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="59" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="58" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875">
-    <cfRule type="duplicateValues" dxfId="57" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="298"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="56" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="55" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B877">
-    <cfRule type="duplicateValues" dxfId="54" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="53" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="52" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B879">
-    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="50" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="49" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="288"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B881">
-    <cfRule type="duplicateValues" dxfId="48" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="47" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="46" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="284"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B882">
-    <cfRule type="duplicateValues" dxfId="45" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="286"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="44" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="43" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884">
-    <cfRule type="duplicateValues" dxfId="42" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="283"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="41" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="40" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B883">
-    <cfRule type="duplicateValues" dxfId="39" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="38" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="37" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B885">
-    <cfRule type="duplicateValues" dxfId="36" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="34" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B886">
-    <cfRule type="duplicateValues" dxfId="33" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="274"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="32" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="31" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B887">
-    <cfRule type="duplicateValues" dxfId="30" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="29" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="28" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B888">
-    <cfRule type="duplicateValues" dxfId="27" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="26" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B889">
-    <cfRule type="duplicateValues" dxfId="24" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="22" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B890">
-    <cfRule type="duplicateValues" dxfId="21" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="246"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B891">
-    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="247"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="243"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B892">
-    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B893">
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B894">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B896">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B880">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="217"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="252" priority="210"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="251" priority="209"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B898">
+    <cfRule type="duplicateValues" dxfId="250" priority="211"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B899">
+    <cfRule type="duplicateValues" dxfId="249" priority="206"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B899">
+    <cfRule type="duplicateValues" dxfId="248" priority="207"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B899">
+    <cfRule type="duplicateValues" dxfId="247" priority="208"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B900">
+    <cfRule type="duplicateValues" dxfId="240" priority="197"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B900">
+    <cfRule type="duplicateValues" dxfId="239" priority="198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B900">
+    <cfRule type="duplicateValues" dxfId="238" priority="199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B901">
+    <cfRule type="duplicateValues" dxfId="237" priority="194"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B901">
+    <cfRule type="duplicateValues" dxfId="236" priority="195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B901">
+    <cfRule type="duplicateValues" dxfId="235" priority="196"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B902">
+    <cfRule type="duplicateValues" dxfId="232" priority="189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B902">
+    <cfRule type="duplicateValues" dxfId="231" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B902">
+    <cfRule type="duplicateValues" dxfId="230" priority="191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="229" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="228" priority="187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903">
+    <cfRule type="duplicateValues" dxfId="227" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B904">
+    <cfRule type="duplicateValues" dxfId="223" priority="180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B904">
+    <cfRule type="duplicateValues" dxfId="222" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B904">
+    <cfRule type="duplicateValues" dxfId="221" priority="182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B905">
+    <cfRule type="duplicateValues" dxfId="217" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B905">
+    <cfRule type="duplicateValues" dxfId="216" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B905">
+    <cfRule type="duplicateValues" dxfId="215" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="214" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="213" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907">
+    <cfRule type="duplicateValues" dxfId="212" priority="173"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B906">
+    <cfRule type="duplicateValues" dxfId="211" priority="168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B906">
+    <cfRule type="duplicateValues" dxfId="210" priority="169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B906">
+    <cfRule type="duplicateValues" dxfId="209" priority="170"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="208" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="207" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B909">
+    <cfRule type="duplicateValues" dxfId="206" priority="167"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B908">
+    <cfRule type="duplicateValues" dxfId="205" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B908">
+    <cfRule type="duplicateValues" dxfId="204" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B908">
+    <cfRule type="duplicateValues" dxfId="203" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B910">
+    <cfRule type="duplicateValues" dxfId="196" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B910">
+    <cfRule type="duplicateValues" dxfId="195" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B910">
+    <cfRule type="duplicateValues" dxfId="194" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="193" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="192" priority="151"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B912">
+    <cfRule type="duplicateValues" dxfId="191" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B913">
+    <cfRule type="duplicateValues" dxfId="190" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B913">
+    <cfRule type="duplicateValues" dxfId="189" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B913">
+    <cfRule type="duplicateValues" dxfId="188" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="187" priority="144"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="186" priority="145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914">
+    <cfRule type="duplicateValues" dxfId="185" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B915">
+    <cfRule type="duplicateValues" dxfId="181" priority="138"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B915">
+    <cfRule type="duplicateValues" dxfId="180" priority="139"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B915">
+    <cfRule type="duplicateValues" dxfId="179" priority="140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B916">
+    <cfRule type="duplicateValues" dxfId="178" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B916">
+    <cfRule type="duplicateValues" dxfId="177" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B916">
+    <cfRule type="duplicateValues" dxfId="176" priority="137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B917">
+    <cfRule type="duplicateValues" dxfId="175" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B917">
+    <cfRule type="duplicateValues" dxfId="174" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B918">
+    <cfRule type="duplicateValues" dxfId="173" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B918">
+    <cfRule type="duplicateValues" dxfId="172" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B918">
+    <cfRule type="duplicateValues" dxfId="171" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B919">
+    <cfRule type="duplicateValues" dxfId="170" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B919">
+    <cfRule type="duplicateValues" dxfId="169" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B919">
+    <cfRule type="duplicateValues" dxfId="168" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B920">
+    <cfRule type="duplicateValues" dxfId="161" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B920">
+    <cfRule type="duplicateValues" dxfId="160" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B920">
+    <cfRule type="duplicateValues" dxfId="159" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="158" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="157" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922">
+    <cfRule type="duplicateValues" dxfId="156" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B921">
+    <cfRule type="duplicateValues" dxfId="149" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B921">
+    <cfRule type="duplicateValues" dxfId="148" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B921">
+    <cfRule type="duplicateValues" dxfId="147" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B923">
+    <cfRule type="duplicateValues" dxfId="146" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B923">
+    <cfRule type="duplicateValues" dxfId="145" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B923">
+    <cfRule type="duplicateValues" dxfId="144" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B924">
+    <cfRule type="duplicateValues" dxfId="140" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B924">
+    <cfRule type="duplicateValues" dxfId="139" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B924">
+    <cfRule type="duplicateValues" dxfId="138" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B925">
+    <cfRule type="duplicateValues" dxfId="131" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B925">
+    <cfRule type="duplicateValues" dxfId="130" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B925">
+    <cfRule type="duplicateValues" dxfId="129" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B926">
+    <cfRule type="duplicateValues" dxfId="128" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B926">
+    <cfRule type="duplicateValues" dxfId="127" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B926">
+    <cfRule type="duplicateValues" dxfId="126" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="125" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="124" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929">
+    <cfRule type="duplicateValues" dxfId="123" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="122" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="121" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931">
+    <cfRule type="duplicateValues" dxfId="120" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="119" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="118" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B934">
+    <cfRule type="duplicateValues" dxfId="117" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B935">
+    <cfRule type="duplicateValues" dxfId="113" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B935">
+    <cfRule type="duplicateValues" dxfId="112" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B935">
+    <cfRule type="duplicateValues" dxfId="111" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="110" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="109" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B937">
+    <cfRule type="duplicateValues" dxfId="108" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B936">
+    <cfRule type="duplicateValues" dxfId="104" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B936">
+    <cfRule type="duplicateValues" dxfId="103" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B936">
+    <cfRule type="duplicateValues" dxfId="102" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="98" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="97" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B938">
+    <cfRule type="duplicateValues" dxfId="96" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="92" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="91" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B939">
+    <cfRule type="duplicateValues" dxfId="90" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B940">
+    <cfRule type="duplicateValues" dxfId="83" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B940">
+    <cfRule type="duplicateValues" dxfId="81" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B940">
+    <cfRule type="duplicateValues" dxfId="79" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B941">
+    <cfRule type="duplicateValues" dxfId="71" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B941">
+    <cfRule type="duplicateValues" dxfId="69" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B941">
+    <cfRule type="duplicateValues" dxfId="67" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="53" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="51" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943">
+    <cfRule type="duplicateValues" dxfId="49" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B944">
+    <cfRule type="duplicateValues" dxfId="41" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B944">
+    <cfRule type="duplicateValues" dxfId="39" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B944">
+    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B945">
+    <cfRule type="duplicateValues" dxfId="35" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B945">
+    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B945">
+    <cfRule type="duplicateValues" dxfId="31" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B946">
+    <cfRule type="duplicateValues" dxfId="29" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B946">
+    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B946">
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B947">
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B947">
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B947">
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B948">
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B948">
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B948">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B949">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B949">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B949">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
